--- a/src/attributions/attributions_saliency_traj_393.xlsx
+++ b/src/attributions/attributions_saliency_traj_393.xlsx
@@ -999,1709 +999,1709 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.001215144991874695</v>
+        <v>0.005679804366081953</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01795930787920952</v>
+        <v>0.1321446150541306</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002100460696965456</v>
+        <v>0.07087511569261551</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01304526161402464</v>
+        <v>0.02972006052732468</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006463524885475636</v>
+        <v>0.002570041920989752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005932763684540987</v>
+        <v>0.0576317198574543</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001857492956332862</v>
+        <v>0.004917717538774014</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00360551755875349</v>
+        <v>0.006444009020924568</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005825893953442574</v>
+        <v>0.005837195552885532</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002311141462996602</v>
+        <v>0.02405267581343651</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0123179042711854</v>
+        <v>0.128174364566803</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003923398326151073</v>
+        <v>0.09681444615125656</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007465055678039789</v>
+        <v>0.06214917451143265</v>
       </c>
       <c r="N2" t="n">
-        <v>0.005882724653929472</v>
+        <v>0.03148843720555305</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002175874076783657</v>
+        <v>0.02848753146827221</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002268593292683363</v>
+        <v>0.0002391878515481949</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004009376745671034</v>
+        <v>0.01407268736511469</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004996409639716148</v>
+        <v>0.0228621419519186</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008622369496151805</v>
+        <v>0.003375991014763713</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001593328197486699</v>
+        <v>0.02410466596484184</v>
       </c>
       <c r="U2" t="n">
-        <v>0.000440772797446698</v>
+        <v>0.01603846997022629</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001695829792879522</v>
+        <v>0.001855183742009103</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002378307748585939</v>
+        <v>0.008893271908164024</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0006881433655507863</v>
+        <v>0.04403609037399292</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001855574431829154</v>
+        <v>0.003981466870754957</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00170030863955617</v>
+        <v>0.001287760911509395</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0003393985680304468</v>
+        <v>0.005640082061290741</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003628348233178258</v>
+        <v>0.01749112643301487</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.003398201894015074</v>
+        <v>0.01097198482602835</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.001468581380322576</v>
+        <v>0.01020856481045485</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.004581346642225981</v>
+        <v>0.04792029038071632</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0007023409707471728</v>
+        <v>0.03297531232237816</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002949267160147429</v>
+        <v>0.03096956387162209</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.001153728808276355</v>
+        <v>0.01054570358246565</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.006518520880490541</v>
+        <v>0.002117488998919725</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0003817862016148865</v>
+        <v>0.001699790125712752</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0004343489126767963</v>
+        <v>0.0009861069265753031</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.002334938384592533</v>
+        <v>0.04480405524373055</v>
       </c>
       <c r="AM2" t="n">
-        <v>9.264469554182142e-05</v>
+        <v>0.01181185431778431</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0006512210820801556</v>
+        <v>0.01301268115639687</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.001411322737112641</v>
+        <v>0.04854392260313034</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.002347858157008886</v>
+        <v>0.02913353405892849</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0002179502334911376</v>
+        <v>0.009020237252116203</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.00424429913982749</v>
+        <v>0.001044388161972165</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0008406190318055451</v>
+        <v>0.003942281473428011</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.002239581663161516</v>
+        <v>0.01310640946030617</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.00779130682349205</v>
+        <v>0.09646438807249069</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.001306021003983915</v>
+        <v>0.007447161711752415</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.01074825972318649</v>
+        <v>0.03120074234902859</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.004571780562400818</v>
+        <v>0.03038776479661465</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.008647197857499123</v>
+        <v>0.03665309771895409</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.004307161550968885</v>
+        <v>0.001119401073083282</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.004983177408576012</v>
+        <v>0.007778896018862724</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.002707172883674502</v>
+        <v>0.01750693842768669</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0008095235098153353</v>
+        <v>0.006902405060827732</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0039034029468894</v>
+        <v>0.01903055235743523</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0009217443875968456</v>
+        <v>0.03813713788986206</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.00416363263502717</v>
+        <v>0.01180579699575901</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.005330314394086599</v>
+        <v>0.01346349902451038</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.003977784886956215</v>
+        <v>0.01402892451733351</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.001349142054095864</v>
+        <v>0.003712225239723921</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.003286575665697455</v>
+        <v>0.01886148378252983</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.001642164308577776</v>
+        <v>0.004886585287749767</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.001814036280848086</v>
+        <v>0.004476083442568779</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.001071940059773624</v>
+        <v>0.0243428498506546</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.001992486417293549</v>
+        <v>0.01183253526687622</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.002068536821752787</v>
+        <v>0.0270807184278965</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.001950901234522462</v>
+        <v>0.002532598562538624</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0005671100225299597</v>
+        <v>0.002211364451795816</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0002738336334004998</v>
+        <v>0.01020482368767262</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.003655894426628947</v>
+        <v>0.01005753874778748</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.001397805055603385</v>
+        <v>0.003075121436268091</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.002372008981183171</v>
+        <v>0.00684185978025198</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.005341729149222374</v>
+        <v>0.05120687186717987</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.0001936245535034686</v>
+        <v>0.01602933555841446</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.003143109381198883</v>
+        <v>0.02548399940133095</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.001627823454327881</v>
+        <v>0.01721927896142006</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.001277347793802619</v>
+        <v>0.05844349786639214</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.00084951106691733</v>
+        <v>0.002536675659939647</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.002393877133727074</v>
+        <v>0.001241507474333048</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.001030111452564597</v>
+        <v>0.001260257675312459</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0005126748001202941</v>
+        <v>0.001871177926659584</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.002416215837001801</v>
+        <v>0.04796348512172699</v>
       </c>
       <c r="CF2" t="n">
-        <v>7.375457789748907e-05</v>
+        <v>0.02314307168126106</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.002155855763703585</v>
+        <v>0.01359302364289761</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.001097427564673126</v>
+        <v>3.64879088010639e-05</v>
       </c>
       <c r="CI2" t="n">
-        <v>7.038174953777343e-05</v>
+        <v>0.0005036898655816913</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.0003317796799819916</v>
+        <v>0.001131976721808314</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0007744209142401814</v>
+        <v>0.008545266464352608</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0002343910746276379</v>
+        <v>0.0008493431378155947</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.001502391183748841</v>
+        <v>0.00974435918033123</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.001834475551731884</v>
+        <v>0.02272171713411808</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.000188865655218251</v>
+        <v>0.02961723133921623</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.005348742473870516</v>
+        <v>0.04574348777532578</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.00304900761693716</v>
+        <v>0.02445558831095695</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.003216419368982315</v>
+        <v>0.0236715879291296</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.002571757882833481</v>
+        <v>0.005786473862826824</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.002189269056543708</v>
+        <v>0.01060218922793865</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.00174170034006238</v>
+        <v>0.009059085510671139</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0003234609612263739</v>
+        <v>0.003815918695181608</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.002746600192040205</v>
+        <v>0.04666544497013092</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.0009338140953332186</v>
+        <v>0.02385829389095306</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.002778996014967561</v>
+        <v>0.01309925876557827</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.001033650245517492</v>
+        <v>0.007704164832830429</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0008897219086065888</v>
+        <v>0.003399841487407684</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0002544170711189508</v>
+        <v>0.001577334012836218</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.0007186272414401174</v>
+        <v>0.01067609433084726</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.0002669965324457735</v>
+        <v>0.001603644574061036</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.000494681647978723</v>
+        <v>0.01596150919795036</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.006392441689968109</v>
+        <v>0.05931892618536949</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.0009187408722937107</v>
+        <v>0.02648328244686127</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01037694979459047</v>
+        <v>0.03924421593546867</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.007108371704816818</v>
+        <v>0.03613651916384697</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0003224100219085813</v>
+        <v>0.04241715371608734</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.002083704574033618</v>
+        <v>0.004716054070740938</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.008386341854929924</v>
+        <v>0.04483294486999512</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.002499786671251059</v>
+        <v>0.0002307335380464792</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.001733522047288716</v>
+        <v>0.0009534761775285006</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.002208536490797997</v>
+        <v>0.01095259748399258</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.002474495209753513</v>
+        <v>0.01033803261816502</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.0009315008064731956</v>
+        <v>0.01126657798886299</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0004081060760654509</v>
+        <v>0.01198755297809839</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.002150504849851131</v>
+        <v>0.0157301276922226</v>
       </c>
       <c r="DT2" t="n">
-        <v>6.076752106309868e-05</v>
+        <v>0.0008953409269452095</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.002012413926422596</v>
+        <v>0.00348376133479178</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.00176292285323143</v>
+        <v>0.02387714944779873</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.00112449296284467</v>
+        <v>0.009930429980158806</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.0009409872582182288</v>
+        <v>0.02571225166320801</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.001194763113744557</v>
+        <v>0.03114920109510422</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.002356520155444741</v>
+        <v>0.02532804757356644</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.001434428850188851</v>
+        <v>0.01339759491384029</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.000911853916477412</v>
+        <v>0.006895726080983877</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.000233665166888386</v>
+        <v>0.001135613303631544</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.001144662033766508</v>
+        <v>0.0234507005661726</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.0006788148311898112</v>
+        <v>0.02203101105988026</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.0004680226265918463</v>
+        <v>0.01059331279247999</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.0004839918110519648</v>
+        <v>0.05747340619564056</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.00165072432719171</v>
+        <v>0.01291779801249504</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0006651243311353028</v>
+        <v>0.006244021467864513</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.002480149269104004</v>
+        <v>0.0006183218793012202</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.0008235892164520919</v>
+        <v>0.02178381755948067</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.0001460975327063352</v>
+        <v>0.003621299983933568</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.0007569894660264254</v>
+        <v>0.0047377017326653</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.001187767600640655</v>
+        <v>0.004658020101487637</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.0003279114316683263</v>
+        <v>0.004061495419591665</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.0005853520124219358</v>
+        <v>0.005941950250416994</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.0004883114597760141</v>
+        <v>0.002062662737444043</v>
       </c>
       <c r="ER2" t="n">
-        <v>7.351567910518497e-05</v>
+        <v>0.001762112602591515</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.0004235852975398302</v>
+        <v>0.006021051667630672</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.0007361778989434242</v>
+        <v>0.0003553683636710048</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.002183212898671627</v>
+        <v>0.009523742832243443</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.001334522268734872</v>
+        <v>0.008392748422920704</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.001394204096868634</v>
+        <v>0.01376369502395391</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.0004994389018975198</v>
+        <v>0.001660632900893688</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.002563596935942769</v>
+        <v>0.05251315981149673</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.0001865666708908975</v>
+        <v>0.0221928209066391</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.002212247578427196</v>
+        <v>0.01928337849676609</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.001085394993424416</v>
+        <v>0.001463605207391083</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.0006386303575709462</v>
+        <v>0.00612846901640296</v>
       </c>
       <c r="FD2" t="n">
-        <v>7.298942364286631e-05</v>
+        <v>0.000411235960200429</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.0007615889189764857</v>
+        <v>0.009926524013280869</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.0002057837118627504</v>
+        <v>0.001299357041716576</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.001790620619431138</v>
+        <v>0.003883437253534794</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.002384926658123732</v>
+        <v>0.03916170448064804</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.002087492495775223</v>
+        <v>0.001732390373945236</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.003915723878890276</v>
+        <v>0.0007238755933940411</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.00155274523422122</v>
+        <v>0.02344462648034096</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0005657634465023875</v>
+        <v>0.01972741261124611</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.002449664752930403</v>
+        <v>0.007242843508720398</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.0003196913166902959</v>
+        <v>0.01247792411595583</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.0003371307102497667</v>
+        <v>0.003495527897030115</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.0008697250159457326</v>
+        <v>0.003234523581340909</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.001167161739431322</v>
+        <v>0.03986337780952454</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.002738819690421224</v>
+        <v>0.008113734424114227</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.004635797813534737</v>
+        <v>0.04033980891108513</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.003957860637456179</v>
+        <v>0.03266468271613121</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.001276781549677253</v>
+        <v>0.004722096491605043</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.0006369262700900435</v>
+        <v>0.01102975849062204</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.0003639995120465755</v>
+        <v>0.002796415705233812</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.001517997006885707</v>
+        <v>0.01394546870142221</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.000464907381683588</v>
+        <v>0.02855792827904224</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.0005494322977028787</v>
+        <v>0.03672097623348236</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.0008630820084363222</v>
+        <v>0.06365522742271423</v>
       </c>
       <c r="GB2" t="n">
-        <v>9.939516894519329e-05</v>
+        <v>0.008960441686213017</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.008511697873473167</v>
+        <v>0.005199289415031672</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.001150618423707783</v>
+        <v>0.02509108558297157</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.0004341964668128639</v>
+        <v>0.01712320931255817</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.001139385160058737</v>
+        <v>0.006125775631517172</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.0004853311984334141</v>
+        <v>0.004337925929576159</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0001783400512067601</v>
+        <v>3.406247742532287e-06</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004927667789161205</v>
+        <v>2.110812602040824e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005819296929985285</v>
+        <v>7.010893568804022e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001037799287587404</v>
+        <v>6.166600542201195e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002174584427848458</v>
+        <v>4.953646566718817e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003171642310917377</v>
+        <v>2.351052171434276e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006148841348476708</v>
+        <v>1.069712311618787e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009247728739865124</v>
+        <v>2.434205725876382e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001828010281315073</v>
+        <v>2.231864300483721e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007679733098484576</v>
+        <v>1.861610940068203e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004414606839418411</v>
+        <v>2.573385791038163e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>6.275917257880792e-05</v>
+        <v>9.823538675846066e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009782667038962245</v>
+        <v>1.13256428448949e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00182101596146822</v>
+        <v>3.988516255049035e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00354530056938529</v>
+        <v>2.398099422862288e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003010316577274352</v>
+        <v>2.674062216101447e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.289960194611922e-05</v>
+        <v>3.886073500325438e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005118300323374569</v>
+        <v>9.033806236402597e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.4788265414536e-05</v>
+        <v>1.057111717273074e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0005738955806009471</v>
+        <v>2.448190798531868e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>8.660281309857965e-06</v>
+        <v>3.286020273662871e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0005774048622697592</v>
+        <v>2.293529178132303e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003325776197016239</v>
+        <v>4.296171027817763e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00065200449898839</v>
+        <v>3.777942993110628e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.067538485396653e-05</v>
+        <v>3.769158865907229e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.000528026488609612</v>
+        <v>4.140342753089499e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0001635107328183949</v>
+        <v>2.281753722854774e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0004497300833463669</v>
+        <v>2.117935309797758e-06</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.106064443476498e-05</v>
+        <v>3.159958168907906e-06</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0007699793204665184</v>
+        <v>9.171992587653222e-08</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0004344643675722182</v>
+        <v>7.216694939415902e-06</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.657781053334475e-05</v>
+        <v>2.170233528886456e-06</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0002382521633990109</v>
+        <v>7.627446393598802e-06</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0001182213454740122</v>
+        <v>1.839665287661774e-06</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0002129760978277773</v>
+        <v>1.050600076268893e-05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0005378656787797809</v>
+        <v>1.888800397864543e-06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0006769923493266106</v>
+        <v>3.134030748697114e-06</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0005256002186797559</v>
+        <v>1.502265149611048e-06</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0002292451536050066</v>
+        <v>6.952125204406912e-07</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0001380016619805247</v>
+        <v>3.145354867228889e-06</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0002889129973482341</v>
+        <v>4.909702511213254e-08</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0004100532969459891</v>
+        <v>1.145323722084868e-06</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.671120480750687e-05</v>
+        <v>3.749963468635542e-07</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0003581811906769872</v>
+        <v>5.716779014619533e-06</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0003412072837818414</v>
+        <v>1.572482119627239e-06</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0001262397709069774</v>
+        <v>2.011389028666599e-07</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.003712102770805359</v>
+        <v>2.009401032410096e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0005818194476887584</v>
+        <v>3.898765498888679e-06</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0006359920371323824</v>
+        <v>2.976915538965841e-06</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0003691677702590823</v>
+        <v>7.102582458173856e-06</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0006955263670533895</v>
+        <v>1.170528321381425e-05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0002590841031633317</v>
+        <v>5.153603979124455e-07</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.000450366991572082</v>
+        <v>3.292659584985813e-07</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0001533383037894964</v>
+        <v>1.601851295163215e-06</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0002720382180996239</v>
+        <v>3.499278591334587e-06</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.001253216527402401</v>
+        <v>1.368709945381852e-07</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.001441562315449119</v>
+        <v>3.97635585613898e-06</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0001671823411015794</v>
+        <v>4.128264095015766e-07</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.001640239381231368</v>
+        <v>5.709223387384554e-06</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.002376237884163857</v>
+        <v>3.968470537074609e-06</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0005989716155454516</v>
+        <v>5.652887580254173e-08</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0002318639890290797</v>
+        <v>7.924286364868749e-06</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0002917101373896003</v>
+        <v>3.596917167669744e-06</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0003990164259448647</v>
+        <v>1.010773971188428e-07</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.001034810789860785</v>
+        <v>4.407333108247258e-06</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0004559102817438543</v>
+        <v>2.393541535639088e-06</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0003042501921299845</v>
+        <v>3.668724730232498e-06</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0007790193776600063</v>
+        <v>2.739560613918002e-06</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0008806171827018261</v>
+        <v>5.518211764865555e-06</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0003837022231891751</v>
+        <v>5.056207555753645e-06</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0004709325730800629</v>
+        <v>1.543307803331118e-06</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0004528118879534304</v>
+        <v>5.127108124725055e-06</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.344711745332461e-05</v>
+        <v>1.250738364433346e-06</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.001799190067686141</v>
+        <v>1.046624402079033e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0004377088625915349</v>
+        <v>1.171169969893526e-06</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.0004826828953810036</v>
+        <v>4.397973498271313e-06</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.207512291846797e-05</v>
+        <v>2.0795596356038e-09</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0001170242030639201</v>
+        <v>8.768818588578142e-06</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0001695301616564393</v>
+        <v>3.670156502266764e-06</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0001302698510698974</v>
+        <v>1.214413941852399e-06</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.702742444351315e-06</v>
+        <v>4.116624552352732e-07</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.803934694384225e-05</v>
+        <v>1.218043280459824e-06</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0007345433696173131</v>
+        <v>5.834227522427682e-06</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0003137390303891152</v>
+        <v>2.720985321502667e-06</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0002963859296869487</v>
+        <v>1.63851757406519e-06</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.326198071183171e-05</v>
+        <v>1.08270660348353e-06</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0005168000352568924</v>
+        <v>5.176927516004071e-06</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.000409977394156158</v>
+        <v>2.081194452330237e-07</v>
       </c>
       <c r="CK3" t="n">
-        <v>6.47624401608482e-05</v>
+        <v>1.041331074702612e-06</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.0001200109618366696</v>
+        <v>1.722639922263625e-06</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.001016181311570108</v>
+        <v>6.232791065485799e-07</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0008121446007862687</v>
+        <v>4.553508006210905e-06</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0001198120880872011</v>
+        <v>5.418634373199893e-06</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.0002287540264660493</v>
+        <v>2.626806690386729e-06</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0006704740808345377</v>
+        <v>1.367563299936592e-06</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.0001374456915073097</v>
+        <v>1.362271291327488e-06</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.0008201486198231578</v>
+        <v>1.563112846270087e-06</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.0009173794533126056</v>
+        <v>9.377974492963403e-06</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.0001185802975669503</v>
+        <v>5.237617415332352e-07</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.92956883640727e-05</v>
+        <v>4.125537031995918e-07</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.0005878517404198647</v>
+        <v>5.802603482152335e-06</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0002988293417729437</v>
+        <v>3.07116692965792e-06</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0004767231876030564</v>
+        <v>2.740748186624842e-06</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.841478842834476e-05</v>
+        <v>1.013930500448623e-06</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0005605171900242567</v>
+        <v>5.913885161135113e-06</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0003676687483675778</v>
+        <v>5.760680892308301e-07</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.748404949670658e-05</v>
+        <v>7.053772606013808e-07</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.54731673724018e-05</v>
+        <v>1.326123538092361e-06</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0003110412508249283</v>
+        <v>3.527380840750993e-07</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.0006636973121203482</v>
+        <v>1.027773305395385e-05</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0004248490440659225</v>
+        <v>1.286912493014825e-06</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.000990642118267715</v>
+        <v>1.94869562619715e-06</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0005756057798862457</v>
+        <v>3.937932433473179e-06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>5.356650217436254e-05</v>
+        <v>5.732385488954606e-06</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.0001036272951751016</v>
+        <v>3.637249847088242e-06</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0004662046849261969</v>
+        <v>6.030536042089807e-06</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.000756904948502779</v>
+        <v>5.746425813413225e-06</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.0001021271673380397</v>
+        <v>1.354664220798441e-07</v>
       </c>
       <c r="DO3" t="n">
-        <v>8.531363710062578e-05</v>
+        <v>1.624028413971246e-06</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.0003861448494717479</v>
+        <v>2.128828327840893e-06</v>
       </c>
       <c r="DQ3" t="n">
-        <v>4.748153151012957e-05</v>
+        <v>3.852849204122322e-06</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.000311576877720654</v>
+        <v>3.24745315083419e-06</v>
       </c>
       <c r="DS3" t="n">
-        <v>9.618004696676508e-05</v>
+        <v>3.310616193630267e-06</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0004571497556753457</v>
+        <v>5.11270081915427e-06</v>
       </c>
       <c r="DU3" t="n">
-        <v>3.311270847916603e-05</v>
+        <v>4.797276687895646e-06</v>
       </c>
       <c r="DV3" t="n">
-        <v>4.233002255205065e-05</v>
+        <v>1.258203724319173e-06</v>
       </c>
       <c r="DW3" t="n">
-        <v>2.234475687146187e-05</v>
+        <v>6.980644684517756e-07</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0008353464072570205</v>
+        <v>1.010532400869124e-06</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0002889843017328531</v>
+        <v>3.692258360388223e-06</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.00011404488759581</v>
+        <v>3.06147126138967e-06</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0002286015078425407</v>
+        <v>1.133099885919364e-06</v>
       </c>
       <c r="EB3" t="n">
-        <v>2.273311838507652e-05</v>
+        <v>3.565432393770607e-08</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.570053427712992e-06</v>
+        <v>8.227251555581461e-07</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0005973619408905506</v>
+        <v>2.283237790834391e-06</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.0002694247232284397</v>
+        <v>4.842913313041208e-06</v>
       </c>
       <c r="EF3" t="n">
-        <v>4.913341399515048e-05</v>
+        <v>7.304780638150987e-07</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.0007913319277577102</v>
+        <v>3.550832161636208e-06</v>
       </c>
       <c r="EH3" t="n">
-        <v>2.153174500563182e-05</v>
+        <v>6.003476755722659e-07</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.0003971823607571423</v>
+        <v>1.410028858117585e-06</v>
       </c>
       <c r="EJ3" t="n">
-        <v>6.34982279734686e-06</v>
+        <v>1.371165808450314e-06</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.0008060332620516419</v>
+        <v>1.592273520145682e-06</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.0004577178915496916</v>
+        <v>6.960589189475286e-07</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.0002321830834262073</v>
+        <v>1.673814381319971e-06</v>
       </c>
       <c r="EN3" t="n">
-        <v>5.235691060079262e-05</v>
+        <v>2.7093125254396e-07</v>
       </c>
       <c r="EO3" t="n">
-        <v>8.03443617769517e-05</v>
+        <v>1.860171892076323e-07</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0002060271363006905</v>
+        <v>3.278538315498736e-06</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0004518588830251247</v>
+        <v>3.764175744436216e-06</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.0001465682726120576</v>
+        <v>2.395839828750468e-06</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.0002053776261163875</v>
+        <v>4.420761797518935e-06</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.0006809147889725864</v>
+        <v>3.764646407944383e-06</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.000182965857675299</v>
+        <v>2.478259830240859e-06</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.000791463244240731</v>
+        <v>2.716435801630723e-06</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.0004270111094228923</v>
+        <v>5.703435590476147e-08</v>
       </c>
       <c r="EX3" t="n">
-        <v>9.493473044130951e-05</v>
+        <v>2.138763477432803e-08</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.000579307263251394</v>
+        <v>6.613138339162106e-06</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.0001140032545663416</v>
+        <v>2.412273943264154e-06</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.0003080485621467233</v>
+        <v>3.10020959659596e-06</v>
       </c>
       <c r="FB3" t="n">
-        <v>7.26577709428966e-05</v>
+        <v>2.349191390749183e-06</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.0005958579131402075</v>
+        <v>4.667627763410565e-06</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.0003826168831437826</v>
+        <v>7.583999490634596e-07</v>
       </c>
       <c r="FE3" t="n">
-        <v>7.255340460687876e-05</v>
+        <v>6.538526235999598e-07</v>
       </c>
       <c r="FF3" t="n">
-        <v>9.151997073786333e-05</v>
+        <v>1.341371103080746e-08</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.0002265083167003468</v>
+        <v>3.967366808410588e-07</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.0004516391200013459</v>
+        <v>8.166468433046248e-06</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.0004511470906436443</v>
+        <v>3.358379444762249e-06</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.001043260213918984</v>
+        <v>5.922841410210822e-06</v>
       </c>
       <c r="FK3" t="n">
-        <v>2.583733294159174e-05</v>
+        <v>5.28937471244717e-06</v>
       </c>
       <c r="FL3" t="n">
-        <v>2.955143281724304e-05</v>
+        <v>7.537914370914223e-06</v>
       </c>
       <c r="FM3" t="n">
-        <v>6.668124115094543e-05</v>
+        <v>1.230701514032262e-06</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.0002624416665639728</v>
+        <v>4.532387265498983e-06</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.000795417174231261</v>
+        <v>4.800148872163845e-06</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.0002298826293554157</v>
+        <v>1.214517283187888e-06</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.001424687448889017</v>
+        <v>6.439337994379457e-06</v>
       </c>
       <c r="FR3" t="n">
-        <v>4.197117232251912e-05</v>
+        <v>1.515452368039405e-06</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.0008156292606145144</v>
+        <v>4.247582182870246e-06</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.0001107500283978879</v>
+        <v>1.30055286717834e-06</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.0002101668942486867</v>
+        <v>1.14120302896481e-06</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.0001562230463605374</v>
+        <v>2.07409084396204e-06</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.001063230680301785</v>
+        <v>1.00227489383542e-05</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.0002279898035340011</v>
+        <v>3.132656729576411e-06</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.0008308776887133718</v>
+        <v>7.333676876442041e-06</v>
       </c>
       <c r="FZ3" t="n">
-        <v>4.174972855253145e-05</v>
+        <v>1.228221435667365e-07</v>
       </c>
       <c r="GA3" t="n">
-        <v>7.88627949077636e-06</v>
+        <v>1.198882546304958e-05</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.0001092109232558869</v>
+        <v>1.315829194936669e-06</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.0001629586768103763</v>
+        <v>1.169569986814167e-05</v>
       </c>
       <c r="GD3" t="n">
-        <v>9.525065252091736e-07</v>
+        <v>6.43848807158065e-06</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.0008469669846817851</v>
+        <v>3.331016955598898e-07</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.0008518361719325185</v>
+        <v>3.013822833963786e-06</v>
       </c>
       <c r="GG3" t="n">
-        <v>7.495524187106639e-05</v>
+        <v>1.35049276650534e-06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.00398004287853837</v>
+        <v>0.02692504599690437</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03659386932849884</v>
+        <v>0.8873727321624756</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004232640843838453</v>
+        <v>0.3313296437263489</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01098543964326382</v>
+        <v>0.6749704480171204</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002483980264514685</v>
+        <v>0.1049743220210075</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008733545430004597</v>
+        <v>0.8388251662254333</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001798865618184209</v>
+        <v>0.3304470777511597</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005393845494836569</v>
+        <v>0.2690480947494507</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01011238247156143</v>
+        <v>0.03541837632656097</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005584750790148973</v>
+        <v>0.07741059362888336</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03344957157969475</v>
+        <v>0.9430215358734131</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001014585141092539</v>
+        <v>0.4897443950176239</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01065473351627588</v>
+        <v>0.9210026860237122</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001415127422660589</v>
+        <v>0.2625539302825928</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007289614877663553</v>
+        <v>0.7785300016403198</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002074517775326967</v>
+        <v>0.2657095789909363</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001166949048638344</v>
+        <v>0.1506708711385727</v>
       </c>
       <c r="R4" t="n">
-        <v>0.006212221458554268</v>
+        <v>0.02172302827239037</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005182648543268442</v>
+        <v>0.06068544089794159</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001276178751140833</v>
+        <v>0.01836038008332253</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002600700361654162</v>
+        <v>0.06674394011497498</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002179511357098818</v>
+        <v>0.07349095493555069</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01149260345846415</v>
+        <v>0.1337911039590836</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005776489851996303</v>
+        <v>0.3009069859981537</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.000342662853654474</v>
+        <v>0.03721749782562256</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00717672286555171</v>
+        <v>0.05775619298219681</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002422197954729199</v>
+        <v>0.08544202148914337</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002582950051873922</v>
+        <v>0.1098334789276123</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.004766195081174374</v>
+        <v>0.1202353835105896</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.003845110768452287</v>
+        <v>0.07594329118728638</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.141017027199268e-05</v>
+        <v>0.224774032831192</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003134239697828889</v>
+        <v>0.0251326896250248</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.004899125546216965</v>
+        <v>0.5841794013977051</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.003112563164904714</v>
+        <v>0.04737165570259094</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.006836849730461836</v>
+        <v>0.279348760843277</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004352220334112644</v>
+        <v>0.1243331581354141</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0007988241268321872</v>
+        <v>0.04172749444842339</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.004715161863714457</v>
+        <v>0.3829182982444763</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.00207586120814085</v>
+        <v>0.1079312488436699</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.35942807700485e-06</v>
+        <v>0.1073666736483574</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004390153102576733</v>
+        <v>0.2098610997200012</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.002414361573755741</v>
+        <v>0.09530328959226608</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0004400036414153874</v>
+        <v>0.06663090735673904</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0002718414179980755</v>
+        <v>0.01737582497298717</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.000301430351100862</v>
+        <v>0.1106245517730713</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.000109041720861569</v>
+        <v>0.05594349279999733</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.01807793229818344</v>
+        <v>0.5760507583618164</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002756880596280098</v>
+        <v>0.196842834353447</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.009449001401662827</v>
+        <v>0.3152571320533752</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.01358475908637047</v>
+        <v>0.4389620423316956</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.007693142630159855</v>
+        <v>0.4621023535728455</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.004077163990586996</v>
+        <v>0.02798900753259659</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01000344660133123</v>
+        <v>0.00419115275144577</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.006404458545148373</v>
+        <v>0.0969691127538681</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.002710310276597738</v>
+        <v>0.06489980220794678</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01116941124200821</v>
+        <v>0.005174411460757256</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002061477629467845</v>
+        <v>0.297427773475647</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.003383888863027096</v>
+        <v>0.006884649395942688</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.003470984753221273</v>
+        <v>0.2478444576263428</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.000952593982219696</v>
+        <v>0.1149565875530243</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0002869151649065316</v>
+        <v>0.09324967861175537</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.00337734934873879</v>
+        <v>0.03123960271477699</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.073539457749575e-05</v>
+        <v>0.1315699368715286</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001476802164688706</v>
+        <v>0.02393919602036476</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0001783414627425373</v>
+        <v>0.06801243126392365</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0008032195037230849</v>
+        <v>0.06118148565292358</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.004177652299404144</v>
+        <v>0.09917988628149033</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.004633187316358089</v>
+        <v>0.05799636244773865</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.001259259646758437</v>
+        <v>0.1125925928354263</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.001602309639565647</v>
+        <v>0.03952938318252563</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0008047001902014017</v>
+        <v>0.09201687574386597</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0009714348125271499</v>
+        <v>0.03858183696866035</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.003514137119054794</v>
+        <v>0.0360322967171669</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01210984122008085</v>
+        <v>0.4319663941860199</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0006240817019715905</v>
+        <v>0.1419112235307693</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.008168271742761135</v>
+        <v>0.3167391419410706</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.002834009937942028</v>
+        <v>0.05269976705312729</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001240413286723197</v>
+        <v>0.4051006138324738</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.002003913978114724</v>
+        <v>0.03327323123812675</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.007431773468852043</v>
+        <v>0.05411761626601219</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.004588880110532045</v>
+        <v>0.074842169880867</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001772521412931383</v>
+        <v>0.01356113329529762</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.003995154518634081</v>
+        <v>0.2737454473972321</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0009419058915227652</v>
+        <v>0.09343309700489044</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002196225337684155</v>
+        <v>0.217251256108284</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001503031235188246</v>
+        <v>0.003206216730177402</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001088690711185336</v>
+        <v>0.1902553290128708</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.001729821669869125</v>
+        <v>0.003438238054513931</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0008909520111046731</v>
+        <v>0.1155346408486366</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0005954369553364813</v>
+        <v>0.0403713621199131</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.006368448026478291</v>
+        <v>0.07913802564144135</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0006502859760075808</v>
+        <v>0.09482106566429138</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0003020760195795447</v>
+        <v>0.410925418138504</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.002241804962977767</v>
+        <v>0.2677175402641296</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002718143165111542</v>
+        <v>0.04373524338006973</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.00238377065397799</v>
+        <v>0.03689592331647873</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.006234429776668549</v>
+        <v>0.1555313766002655</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.007329234387725592</v>
+        <v>0.06428290903568268</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.397388405166566e-05</v>
+        <v>0.03682032227516174</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.001523848273791373</v>
+        <v>0.006172920577228069</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.004380371421575546</v>
+        <v>0.235224187374115</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.000155523608555086</v>
+        <v>0.1119874119758606</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.00228558387607336</v>
+        <v>0.23525270819664</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.001338270376436412</v>
+        <v>0.08954852074384689</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.001248501357622445</v>
+        <v>0.2108265310525894</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001683600246906281</v>
+        <v>0.008822528645396233</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.00141224660910666</v>
+        <v>0.1326283365488052</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.001473606564104557</v>
+        <v>0.01669961959123611</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.005610877647995949</v>
+        <v>0.1209938749670982</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.00257284939289093</v>
+        <v>0.1335316300392151</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.002777513116598129</v>
+        <v>0.005127504467964172</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.009956941939890385</v>
+        <v>0.2200818210840225</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.00826428085565567</v>
+        <v>0.00349840335547924</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0008479625685140491</v>
+        <v>0.6349266767501831</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.005909428000450134</v>
+        <v>0.0007063373923301697</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.003790452610701323</v>
+        <v>0.4601053893566132</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001533572794869542</v>
+        <v>0.04761023819446564</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.004592109471559525</v>
+        <v>0.05381395667791367</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.00413045659661293</v>
+        <v>0.2028598189353943</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0008484710706397891</v>
+        <v>0.02178877219557762</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.521315425634384e-05</v>
+        <v>0.09008131921291351</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.001900938572362065</v>
+        <v>0.005028011277318001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.008207136765122414</v>
+        <v>0.04434436187148094</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.00354732945561409</v>
+        <v>0.07841221988201141</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.004103331360965967</v>
+        <v>0.1450706571340561</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0001516274642199278</v>
+        <v>0.2249358892440796</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.00499797286465764</v>
+        <v>0.003099158406257629</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.002064626896753907</v>
+        <v>0.1400875747203827</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.001693029538728297</v>
+        <v>0.2856953144073486</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.001468354603275657</v>
+        <v>0.05754072219133377</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.001724809058941901</v>
+        <v>0.1060576587915421</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.002983631566166878</v>
+        <v>0.1955224871635437</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.002427461557090282</v>
+        <v>0.08665323257446289</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.002378201112151146</v>
+        <v>0.4062776863574982</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.005382924806326628</v>
+        <v>0.404727965593338</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.001448370283469558</v>
+        <v>0.04496777802705765</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001912121428176761</v>
+        <v>0.1271328777074814</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0004223588621243834</v>
+        <v>0.1200508028268814</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001224049599841237</v>
+        <v>0.185157909989357</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.002120348159223795</v>
+        <v>0.1114462614059448</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.002335653640329838</v>
+        <v>0.1891757696866989</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0001615629298612475</v>
+        <v>0.003194844350218773</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0006337320664897561</v>
+        <v>0.05347819626331329</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0006351774791255593</v>
+        <v>0.004334820900112391</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.002854818711057305</v>
+        <v>0.007226027548313141</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.003380886977538466</v>
+        <v>0.189522922039032</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.00121031841263175</v>
+        <v>0.1002205461263657</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0009753951453603804</v>
+        <v>0.1723481863737106</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.002857703948393464</v>
+        <v>0.01608743518590927</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.01122666709125042</v>
+        <v>0.03321385011076927</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.002300477121025324</v>
+        <v>0.1273802667856216</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.003293562447652221</v>
+        <v>0.119425356388092</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001624055905267596</v>
+        <v>0.14534892141819</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.002086587948724627</v>
+        <v>0.006256780121475458</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.00453902268782258</v>
+        <v>0.2846506237983704</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0008337250910699368</v>
+        <v>0.07530666142702103</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.00210784375667572</v>
+        <v>0.2478058785200119</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0009129183599725366</v>
+        <v>0.005805595777928829</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.001256604213267565</v>
+        <v>0.2147004753351212</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.001501026563346386</v>
+        <v>0.01280024740844965</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.0005389312282204628</v>
+        <v>0.1191969364881516</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0009228219278156757</v>
+        <v>0.032719936221838</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0001148780065705068</v>
+        <v>0.0009392499923706055</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0009185753879137337</v>
+        <v>0.02972307056188583</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.004006281495094299</v>
+        <v>0.1080166026949883</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.001374949817545712</v>
+        <v>0.1400242447853088</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.003275040304288268</v>
+        <v>0.04862824082374573</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.001192827126942575</v>
+        <v>0.2321706414222717</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.00149119074922055</v>
+        <v>0.009994197636842728</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.002866942901164293</v>
+        <v>0.1017144992947578</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.004196170717477798</v>
+        <v>0.1513874381780624</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.002307931426912546</v>
+        <v>0.2491781711578369</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.009217929095029831</v>
+        <v>0.1462060809135437</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.001634357031434774</v>
+        <v>0.3647947907447815</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.001712916768155992</v>
+        <v>0.1206618547439575</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.009267223998904228</v>
+        <v>0.1424012929201126</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.004475508816540241</v>
+        <v>0.1896097213029861</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.000819479813799262</v>
+        <v>0.05695166066288948</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.002299543470144272</v>
+        <v>0.2752688527107239</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.003230968955904245</v>
+        <v>0.01218495145440102</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.001207862747833133</v>
+        <v>0.008401762694120407</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0008072555065155029</v>
+        <v>0.11646818369627</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.001824188278988004</v>
+        <v>0.184424102306366</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.001681042136624455</v>
+        <v>0.1496322900056839</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.01260822638869286</v>
+        <v>0.4115643501281738</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.002427856670692563</v>
+        <v>0.3022678196430206</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.003897917456924915</v>
+        <v>0.2195946127176285</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.004965947475284338</v>
+        <v>0.09755367040634155</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.001871315995231271</v>
+        <v>0.06696821004152298</v>
       </c>
     </row>
     <row r="5">
@@ -3275,1140 +3275,1140 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0003186540561728179</v>
+        <v>0.008290763013064861</v>
       </c>
       <c r="B6" t="n">
-        <v>0.004092548508197069</v>
+        <v>0.07175834476947784</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005115841631777585</v>
+        <v>0.02605240233242512</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001212428556755185</v>
+        <v>0.01473662070930004</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001880763215012848</v>
+        <v>0.007335791364312172</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0006514106644317508</v>
+        <v>0.06270594149827957</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000405859318561852</v>
+        <v>0.007251633331179619</v>
       </c>
       <c r="H6" t="n">
-        <v>1.522079037385993e-05</v>
+        <v>0.03597370907664299</v>
       </c>
       <c r="I6" t="n">
-        <v>9.815646626520902e-05</v>
+        <v>0.009497106075286865</v>
       </c>
       <c r="J6" t="n">
-        <v>6.62874081172049e-05</v>
+        <v>0.01356360223144293</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002639419864863157</v>
+        <v>0.09050130844116211</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004057526821270585</v>
+        <v>0.0309711080044508</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001059163711033762</v>
+        <v>0.01915645599365234</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002139510586857796</v>
+        <v>0.006660101935267448</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0007235259981825948</v>
+        <v>0.05054319649934769</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0004483568482100964</v>
+        <v>0.01190161798149347</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0007457278552465141</v>
+        <v>0.004293310455977917</v>
       </c>
       <c r="R6" t="n">
-        <v>5.694572610082105e-05</v>
+        <v>0.0207328237593174</v>
       </c>
       <c r="S6" t="n">
-        <v>4.590798198478296e-05</v>
+        <v>0.006019582506269217</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0008311346755363047</v>
+        <v>0.01958939433097839</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0003387146280147135</v>
+        <v>0.002241397276520729</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005165905458852649</v>
+        <v>0.01225528307259083</v>
       </c>
       <c r="W6" t="n">
-        <v>0.000106646868516691</v>
+        <v>0.005318685434758663</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0005927015445195138</v>
+        <v>0.006318174302577972</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001682635047473013</v>
+        <v>0.003310228232294321</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0004263409646227956</v>
+        <v>0.007328042294830084</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001592872431501746</v>
+        <v>0.00678762374445796</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.526086220517755e-05</v>
+        <v>0.007196818944066763</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0007677724934183061</v>
+        <v>0.002671632915735245</v>
       </c>
       <c r="AD6" t="n">
-        <v>6.607199611607939e-05</v>
+        <v>0.001711006043478847</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.016977850871626e-05</v>
+        <v>0.02042019739747047</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0001452694123145193</v>
+        <v>0.03230270743370056</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.873647074215114e-07</v>
+        <v>0.003337505273520947</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0005595881375484169</v>
+        <v>0.003932759165763855</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.405303530395031e-05</v>
+        <v>0.01490024570375681</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0001301371230510995</v>
+        <v>0.0009704271797090769</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0003193412267137319</v>
+        <v>0.008474113419651985</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0006750444881618023</v>
+        <v>0.01119723543524742</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0002655090938787907</v>
+        <v>0.001380503410473466</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0001102364039979875</v>
+        <v>0.01775996200740337</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.000480237154988572</v>
+        <v>0.003852003021165729</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0007235553348436952</v>
+        <v>0.005987043492496014</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0001922782248584554</v>
+        <v>0.006790285930037498</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.478901685914025e-05</v>
+        <v>0.01925242319703102</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0001836511364672333</v>
+        <v>0.002757490612566471</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0004981246893294156</v>
+        <v>0.01108965836465359</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.003314241766929626</v>
+        <v>0.08048390597105026</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.0002080645499518141</v>
+        <v>0.007703003473579884</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.950619328767061e-05</v>
+        <v>0.002433771966025233</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0001783945772331208</v>
+        <v>0.01705260388553143</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0003404316958039999</v>
+        <v>0.02560607902705669</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.542110688518733e-05</v>
+        <v>0.001361452275887132</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.000497628643643111</v>
+        <v>0.003430805867537856</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0002251709520351142</v>
+        <v>0.008845045231282711</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.866397360572591e-05</v>
+        <v>0.01189218275249004</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.000590923591516912</v>
+        <v>0.008500806987285614</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0003357896057423204</v>
+        <v>0.004748704843223095</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0005695988074876368</v>
+        <v>0.01647747308015823</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.001554863178171217</v>
+        <v>0.01248331181704998</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0002341830258956179</v>
+        <v>0.01297655422240496</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0004022635112050921</v>
+        <v>0.003537644166499376</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0008345082751475275</v>
+        <v>0.01525689288973808</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.919626760762185e-05</v>
+        <v>0.01210871152579784</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0004020005872007459</v>
+        <v>0.0004943646490573883</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.001214139512740076</v>
+        <v>0.006503672804683447</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.000239555025473237</v>
+        <v>0.01240055821835995</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0005529966438189149</v>
+        <v>0.0145301278680563</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.001055708155035973</v>
+        <v>0.02379740588366985</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0005462249391712248</v>
+        <v>0.01369205396622419</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0001943672978086397</v>
+        <v>0.00835954025387764</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0001641629205550998</v>
+        <v>0.01116321980953217</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.826214353670366e-05</v>
+        <v>0.01397185306996107</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0004047001129947603</v>
+        <v>0.01815080642700195</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.001857700408436358</v>
+        <v>0.056838758289814</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0005908128223381937</v>
+        <v>0.006173853296786547</v>
       </c>
       <c r="BX6" t="n">
-        <v>7.327832281589508e-05</v>
+        <v>0.01025756727904081</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0004050538700539619</v>
+        <v>0.005650593433529139</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0009724036208353937</v>
+        <v>0.01235281955450773</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0004230431804899126</v>
+        <v>0.01310429163277149</v>
       </c>
       <c r="CB6" t="n">
-        <v>8.018985681701452e-05</v>
+        <v>0.003743224078789353</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.633309385506436e-05</v>
+        <v>0.000900556449778378</v>
       </c>
       <c r="CD6" t="n">
-        <v>7.222985732369125e-05</v>
+        <v>0.00886046513915062</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0007381530595012009</v>
+        <v>0.01747720316052437</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.400850255275145e-05</v>
+        <v>0.005412200931459665</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0002939848636742681</v>
+        <v>0.0008757193572819233</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0001206463857670315</v>
+        <v>0.0006705396808683872</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.0002219291491201147</v>
+        <v>0.01377387717366219</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0001492998853791505</v>
+        <v>0.0008906382136046886</v>
       </c>
       <c r="CK6" t="n">
-        <v>5.03351548104547e-05</v>
+        <v>0.006685058586299419</v>
       </c>
       <c r="CL6" t="n">
-        <v>5.174683974473737e-05</v>
+        <v>0.001398720312863588</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.000764307682402432</v>
+        <v>0.008664322085678577</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0005531723727472126</v>
+        <v>0.03129471838474274</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0002158850838895887</v>
+        <v>0.01829102449119091</v>
       </c>
       <c r="CP6" t="n">
-        <v>5.914749635849148e-05</v>
+        <v>0.00415175873786211</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0005810664733871818</v>
+        <v>0.03037119284272194</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0004673563234973699</v>
+        <v>0.01189915463328362</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0001303037570323795</v>
+        <v>0.0005794435273855925</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0004268303164280951</v>
+        <v>0.006026869639754295</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0002689890388865024</v>
+        <v>0.002042939653620124</v>
       </c>
       <c r="CV6" t="n">
-        <v>8.050693577388301e-05</v>
+        <v>0.003132764250040054</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0004924479871988297</v>
+        <v>0.01676299050450325</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.0001566281571285799</v>
+        <v>0.004599604289978743</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0004854049475397915</v>
+        <v>0.001406667288392782</v>
       </c>
       <c r="CZ6" t="n">
-        <v>9.570152178639546e-05</v>
+        <v>0.0001992137404158711</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0003334076900500804</v>
+        <v>0.01310904882848263</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0001375325955450535</v>
+        <v>0.003395460546016693</v>
       </c>
       <c r="DC6" t="n">
-        <v>3.17244375764858e-05</v>
+        <v>0.006122243590652943</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.232002488104627e-05</v>
+        <v>0.001290841493755579</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0004649999318644404</v>
+        <v>0.003937249071896076</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.001918787718750536</v>
+        <v>0.04263293743133545</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.655595744727179e-05</v>
+        <v>0.0156687069684267</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.001030662329867482</v>
+        <v>0.003180526662617922</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0005878699012100697</v>
+        <v>0.008381124585866928</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.000112928195449058</v>
+        <v>0.0318039208650589</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.001098057138733566</v>
+        <v>0.001928494544699788</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0001846669474616647</v>
+        <v>0.01242582406848669</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0002925548178609461</v>
+        <v>0.02760306745767593</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0007619863608852029</v>
+        <v>0.002242187038064003</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0006914300029166043</v>
+        <v>0.01573022082448006</v>
       </c>
       <c r="DP6" t="n">
-        <v>5.289090040605515e-05</v>
+        <v>0.007400517351925373</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0004997548530809581</v>
+        <v>0.008834020234644413</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.68574178032577e-05</v>
+        <v>0.001193201867863536</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.000199239031644538</v>
+        <v>0.001517433673143387</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.0001346401404589415</v>
+        <v>0.001258742297068238</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0003960008325520903</v>
+        <v>0.01194080431014299</v>
       </c>
       <c r="DV6" t="n">
-        <v>1.952576167241205e-05</v>
+        <v>7.580711098853499e-05</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.0001094414765248075</v>
+        <v>0.0120016485452652</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0002084380685118958</v>
+        <v>0.006539694964885712</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0003274720802437514</v>
+        <v>0.003528475761413574</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0004115364572498947</v>
+        <v>0.001184761058539152</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0008011800819076598</v>
+        <v>0.01865613646805286</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0003397295949980617</v>
+        <v>0.01035995781421661</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.0001996167266042903</v>
+        <v>0.00509552750736475</v>
       </c>
       <c r="ED6" t="n">
-        <v>6.637444312218577e-05</v>
+        <v>0.002088163513690233</v>
       </c>
       <c r="EE6" t="n">
-        <v>1.353842890239321e-05</v>
+        <v>0.01242299936711788</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0002711463603191078</v>
+        <v>0.01271287351846695</v>
       </c>
       <c r="EG6" t="n">
-        <v>7.295847899513319e-05</v>
+        <v>0.01316263992339373</v>
       </c>
       <c r="EH6" t="n">
-        <v>6.510633829748258e-05</v>
+        <v>0.00185948284342885</v>
       </c>
       <c r="EI6" t="n">
-        <v>7.367460057139397e-06</v>
+        <v>0.008444149978458881</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0002338291524210945</v>
+        <v>0.002940885256975889</v>
       </c>
       <c r="EK6" t="n">
-        <v>9.641003998694941e-06</v>
+        <v>0.004869121126830578</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0002493398787919432</v>
+        <v>0.002406958257779479</v>
       </c>
       <c r="EM6" t="n">
-        <v>3.933677362510934e-05</v>
+        <v>0.001892529428005219</v>
       </c>
       <c r="EN6" t="n">
-        <v>1.195574532175669e-05</v>
+        <v>0.001791489310562611</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0005155570688657463</v>
+        <v>0.003878570161759853</v>
       </c>
       <c r="EP6" t="n">
-        <v>9.66937659541145e-05</v>
+        <v>0.003433185629546642</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0002499773981980979</v>
+        <v>0.004588733892887831</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0005004553822800517</v>
+        <v>0.01833699643611908</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0002204651536885649</v>
+        <v>0.03802643343806267</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0009455401450395584</v>
+        <v>0.02174240350723267</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0001212281495099887</v>
+        <v>0.00898347795009613</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.0001778235018718988</v>
+        <v>0.004351099021732807</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0001906540564959869</v>
+        <v>0.004087924491614103</v>
       </c>
       <c r="EX6" t="n">
-        <v>8.721918129594997e-05</v>
+        <v>0.006121310871094465</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0004417955933604389</v>
+        <v>0.02134320139884949</v>
       </c>
       <c r="EZ6" t="n">
-        <v>2.313748882443178e-05</v>
+        <v>0.005463553126901388</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0003863034653477371</v>
+        <v>7.212534546852112e-05</v>
       </c>
       <c r="FB6" t="n">
-        <v>5.463717025122605e-05</v>
+        <v>0.001051762839779258</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.000357942160917446</v>
+        <v>0.01330486685037613</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0001779897575033829</v>
+        <v>0.0002299293410032988</v>
       </c>
       <c r="FE6" t="n">
-        <v>2.568182208051439e-05</v>
+        <v>0.005674379412084818</v>
       </c>
       <c r="FF6" t="n">
-        <v>7.929016283014789e-05</v>
+        <v>0.002968848217278719</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0002592837845440954</v>
+        <v>0.00200525694526732</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0005062047275714576</v>
+        <v>0.02095583826303482</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0001497093180660158</v>
+        <v>0.01145818550139666</v>
       </c>
       <c r="FJ6" t="n">
-        <v>2.864380439859815e-05</v>
+        <v>0.01221091486513615</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0003339334507472813</v>
+        <v>0.01896612532436848</v>
       </c>
       <c r="FL6" t="n">
-        <v>4.735461698146537e-05</v>
+        <v>0.02017955854535103</v>
       </c>
       <c r="FM6" t="n">
-        <v>6.17537516518496e-05</v>
+        <v>0.00777358328923583</v>
       </c>
       <c r="FN6" t="n">
-        <v>1.708326817606576e-05</v>
+        <v>0.02812830731272697</v>
       </c>
       <c r="FO6" t="n">
-        <v>3.10882278427016e-05</v>
+        <v>0.008700825273990631</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0005623201723210514</v>
+        <v>0.02738481760025024</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.0003725503338500857</v>
+        <v>0.008037135004997253</v>
       </c>
       <c r="FR6" t="n">
-        <v>6.978950113989413e-05</v>
+        <v>0.01729520782828331</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0004713781818281859</v>
+        <v>0.02285699173808098</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.00142721354495734</v>
+        <v>0.03758438676595688</v>
       </c>
       <c r="FU6" t="n">
-        <v>4.509139034780674e-05</v>
+        <v>0.0005576503463089466</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0002459916286170483</v>
+        <v>0.01456991583108902</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0002527271863073111</v>
+        <v>0.02789116278290749</v>
       </c>
       <c r="FX6" t="n">
-        <v>4.744761099573225e-05</v>
+        <v>0.003166616894304752</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.0001467526017222553</v>
+        <v>0.02614434622228146</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.0007122766110114753</v>
+        <v>0.0181118156760931</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0002104996237903833</v>
+        <v>0.008695715107023716</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0003018908319063485</v>
+        <v>0.0157668199390173</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.000374739378457889</v>
+        <v>0.0152784800156951</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0006488955114036798</v>
+        <v>0.00428770249709487</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0006307339644990861</v>
+        <v>0.007284997031092644</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0004040390194859356</v>
+        <v>0.01966633461415768</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0002305052330484614</v>
+        <v>0.009642136283218861</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2.78918378171511e-05</v>
+        <v>0.005475640296936035</v>
       </c>
       <c r="B7" t="n">
-        <v>0.005210076458752155</v>
+        <v>0.01452834531664848</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0004208498867228627</v>
+        <v>0.001454053446650505</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003014142857864499</v>
+        <v>0.02978680655360222</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008912230841815472</v>
+        <v>0.006042215041816235</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0004817098961211741</v>
+        <v>0.02098350413143635</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005420346860773861</v>
+        <v>0.01914365403354168</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0005552138900384307</v>
+        <v>0.02112322859466076</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003040781593881547</v>
+        <v>0.005172473378479481</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0005570349167101085</v>
+        <v>0.003274021437391639</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00369690265506506</v>
+        <v>0.00811447761952877</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001336867862846702</v>
+        <v>0.001891662366688251</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002789786783978343</v>
+        <v>0.04215258359909058</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001656508073210716</v>
+        <v>0.01501956861466169</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001222898368723691</v>
+        <v>0.02253664657473564</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0002688367676455528</v>
+        <v>0.02367889881134033</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0003061383322346956</v>
+        <v>0.01318053156137466</v>
       </c>
       <c r="R7" t="n">
-        <v>3.162509528920054e-06</v>
+        <v>0.003023482160642743</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002255481231259182</v>
+        <v>0.004491899628192186</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001012777909636497</v>
+        <v>0.0003649645368568599</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001981313980650157</v>
+        <v>0.003590844105929136</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0005192059325054288</v>
+        <v>0.0009740814566612244</v>
       </c>
       <c r="W7" t="n">
-        <v>2.436129580019042e-05</v>
+        <v>0.004377315752208233</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0006676185876131058</v>
+        <v>0.005983445793390274</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0005522912251763046</v>
+        <v>0.0004154761554673314</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0002727021346800029</v>
+        <v>0.006065721623599529</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0003582920471671969</v>
+        <v>0.0001417057355865836</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0005017836228944361</v>
+        <v>0.004384778439998627</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.001040791277773678</v>
+        <v>0.003210304770618677</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0001318476861342788</v>
+        <v>0.00544655229896307</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.502975646872073e-05</v>
+        <v>4.714471288025379e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.000410841079428792</v>
+        <v>0.006535243708640337</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001347681827610359</v>
+        <v>0.009637122973799706</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0001738855644362047</v>
+        <v>0.002138712909072638</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0001957959611900151</v>
+        <v>0.007518324069678783</v>
       </c>
       <c r="AJ7" t="n">
-        <v>9.716170461615548e-05</v>
+        <v>0.00462640542536974</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0003388368641026318</v>
+        <v>0.004396048840135336</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0004698047123383731</v>
+        <v>0.008245484903454781</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0001851955312304199</v>
+        <v>0.006234501488506794</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0001629266625968739</v>
+        <v>0.005493305623531342</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.000659769109915942</v>
+        <v>0.000666443957015872</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0005204962799325585</v>
+        <v>0.005867253988981247</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0002687385713215917</v>
+        <v>0.006671402603387833</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.000298759201541543</v>
+        <v>0.004178651608526707</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0002139188145520166</v>
+        <v>0.001175355864688754</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0005253132549114525</v>
+        <v>0.008642138913273811</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.004002860281616449</v>
+        <v>0.008345022797584534</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0002367648266954347</v>
+        <v>0.009031332097947598</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.000448419654276222</v>
+        <v>0.01005395594984293</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0002826930431183428</v>
+        <v>0.02513883076608181</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0001222278515342623</v>
+        <v>0.01816827431321144</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.239181286422536e-05</v>
+        <v>0.003279116936028004</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0002101837744703516</v>
+        <v>0.003370840102434158</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.564588642911986e-05</v>
+        <v>0.00424546655267477</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0002298754843650386</v>
+        <v>0.001912394538521767</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.000905645196326077</v>
+        <v>0.002024909015744925</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.001034985296428204</v>
+        <v>0.0004285546019673347</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0005982050206512213</v>
+        <v>0.001716510159894824</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.001488585025072098</v>
+        <v>0.009970500133931637</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0005505772423930466</v>
+        <v>0.0009014241513796151</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.000490587844979018</v>
+        <v>0.00414266437292099</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0004253236693330109</v>
+        <v>0.008655047044157982</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0001005513913696632</v>
+        <v>0.002589825075119734</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0007485791575163603</v>
+        <v>0.0004087703418917954</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.001281539909541607</v>
+        <v>0.006181889679282904</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.00052640464855358</v>
+        <v>0.001802695682272315</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.000107223677332513</v>
+        <v>0.008125067688524723</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0006702861282974482</v>
+        <v>0.002218296751379967</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0005716145387850702</v>
+        <v>0.001622089534066617</v>
       </c>
       <c r="BR7" t="n">
-        <v>4.978671495337039e-05</v>
+        <v>0.0009171710698865354</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.00021809694590047</v>
+        <v>0.001492055831477046</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0002179806906497106</v>
+        <v>0.001907473197206855</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0003610792919062078</v>
+        <v>0.002625864231958985</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.002003242960199714</v>
+        <v>0.007461319677531719</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0005038738017901778</v>
+        <v>0.003729882650077343</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0004168159503024071</v>
+        <v>0.01427855901420116</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.000215879874303937</v>
+        <v>0.005403118208050728</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0008302560891024768</v>
+        <v>0.009943022392690182</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0002525883610360324</v>
+        <v>0.003158033359795809</v>
       </c>
       <c r="CB7" t="n">
-        <v>8.751085260882974e-05</v>
+        <v>0.003280462697148323</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0003294898779131472</v>
+        <v>0.0004619492101483047</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0001816370786400512</v>
+        <v>6.260999361984432e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0009147225064225495</v>
+        <v>0.003421259578317404</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0003367456374689937</v>
+        <v>0.0001143749104812741</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0002204436168540269</v>
+        <v>0.010942074470222</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0002208732475992292</v>
+        <v>0.001026254496537149</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.000177223191712983</v>
+        <v>0.003919973038136959</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0001574654597789049</v>
+        <v>0.001175619778223336</v>
       </c>
       <c r="CK7" t="n">
-        <v>2.643277184688486e-05</v>
+        <v>0.004014901351183653</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0002190446830354631</v>
+        <v>0.001258655916899443</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0009559726458974183</v>
+        <v>0.0005086299497634172</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0008382261730730534</v>
+        <v>0.0002899087266996503</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0002723449724726379</v>
+        <v>0.009630009531974792</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.001232554321177304</v>
+        <v>0.01372523885220289</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0008772949804551899</v>
+        <v>0.002352756215259433</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0006131136906333268</v>
+        <v>0.0005432022735476494</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0006439337157644331</v>
+        <v>0.00610489584505558</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0008770506829023361</v>
+        <v>0.002764228731393814</v>
       </c>
       <c r="CU7" t="n">
-        <v>5.939398761256598e-05</v>
+        <v>0.002999168820679188</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0001780903694452718</v>
+        <v>0.0005474400240927935</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.0007607594016008079</v>
+        <v>0.002683218335732818</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0004353605909273028</v>
+        <v>0.0008189345244318247</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0004872205317951739</v>
+        <v>0.01206900738179684</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0002638742735143751</v>
+        <v>0.003964313305914402</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0002265194925712422</v>
+        <v>0.004383980296552181</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0001721735898172483</v>
+        <v>0.001823923899792135</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.000136007642140612</v>
+        <v>0.00377454818226397</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0001752873213263229</v>
+        <v>0.002287432784214616</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0003331997722852975</v>
+        <v>0.005260850302875042</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.000776281114667654</v>
+        <v>0.004897510632872581</v>
       </c>
       <c r="DG7" t="n">
-        <v>8.017869549803436e-05</v>
+        <v>0.0009371456690132618</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.0009403236326761544</v>
+        <v>0.009289933368563652</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0002064547734335065</v>
+        <v>0.00297581497579813</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0001878282346297055</v>
+        <v>0.01685149595141411</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0005955584347248077</v>
+        <v>0.004107832442969084</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.000102331701782532</v>
+        <v>0.01538193039596081</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0001220896519953385</v>
+        <v>0.006830609869211912</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.000253706966759637</v>
+        <v>0.004857457242906094</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0002459887764416635</v>
+        <v>0.00445692939683795</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0005396072519943118</v>
+        <v>0.0008302677888423204</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0001193088974105194</v>
+        <v>0.0007915417663753033</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.000468472542706877</v>
+        <v>0.00322934309951961</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0002951868809759617</v>
+        <v>0.004487850703299046</v>
       </c>
       <c r="DT7" t="n">
-        <v>9.248306741937995e-05</v>
+        <v>0.001195917837321758</v>
       </c>
       <c r="DU7" t="n">
-        <v>2.662078259163536e-05</v>
+        <v>0.007747001945972443</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0003062364994548261</v>
+        <v>0.01222211215645075</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0001524042017990723</v>
+        <v>0.002095302334055305</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0003193509764969349</v>
+        <v>0.002783493604511023</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.000477619789307937</v>
+        <v>0.008541365154087543</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.00015574338613078</v>
+        <v>0.005382627714425325</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0005289659020490944</v>
+        <v>0.0006527256336994469</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0001315373665420339</v>
+        <v>0.007163951639086008</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0001647153694648296</v>
+        <v>0.002151563763618469</v>
       </c>
       <c r="ED7" t="n">
-        <v>1.357379733235575e-05</v>
+        <v>0.009673213586211205</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.633179635973647e-06</v>
+        <v>0.008612325415015221</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0001431284035788849</v>
+        <v>0.005753982812166214</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.000494997831992805</v>
+        <v>0.0004127572756260633</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0002290081174578518</v>
+        <v>0.005058115348219872</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0004492556618060917</v>
+        <v>0.0112502183765173</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.000318948325002566</v>
+        <v>0.0008980212151072919</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0001527151616755873</v>
+        <v>0.002984272781759501</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.0001728929055389017</v>
+        <v>2.629775553941727e-05</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0001037023612298071</v>
+        <v>0.001455198042094707</v>
       </c>
       <c r="EN7" t="n">
-        <v>9.434476669412106e-05</v>
+        <v>0.001039933296851814</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0002943945000879467</v>
+        <v>0.0007071602158248425</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0007279895362444222</v>
+        <v>0.006041408516466618</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.0002987654879689217</v>
+        <v>0.0001100334338843822</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0003610089188441634</v>
+        <v>0.01157799549400806</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0003007441991940141</v>
+        <v>0.001053206855431199</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0005074007785879076</v>
+        <v>0.001547129475511611</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.000508638215251267</v>
+        <v>0.003259278833866119</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.0002777944609988481</v>
+        <v>0.004421613644808531</v>
       </c>
       <c r="EW7" t="n">
-        <v>7.067857950460166e-05</v>
+        <v>0.009747226722538471</v>
       </c>
       <c r="EX7" t="n">
-        <v>1.669690027483739e-05</v>
+        <v>5.129174678586423e-05</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0007782176253385842</v>
+        <v>0.004202257841825485</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0002623012405820191</v>
+        <v>0.0005201692692935467</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0003606658719945699</v>
+        <v>0.01201754063367844</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0001716882106848061</v>
+        <v>0.001486724708229303</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.0003250377776566893</v>
+        <v>0.004272424150258303</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0002174800029024482</v>
+        <v>0.001894802087917924</v>
       </c>
       <c r="FE7" t="n">
-        <v>6.529565143864602e-05</v>
+        <v>0.004347871989011765</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.0002530165656935424</v>
+        <v>0.0002233313280157745</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0002229143719887361</v>
+        <v>0.001184710301458836</v>
       </c>
       <c r="FH7" t="n">
-        <v>4.260151035850868e-05</v>
+        <v>0.000782652641646564</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.0003383861039765179</v>
+        <v>0.003499303013086319</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.0005344368983060122</v>
+        <v>0.004561888985335827</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0003316332004033029</v>
+        <v>0.0008489970932714641</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.0001921970106195658</v>
+        <v>0.0004898973274976015</v>
       </c>
       <c r="FM7" t="n">
-        <v>5.567001790041104e-05</v>
+        <v>0.001283616642467678</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.0002022594126174226</v>
+        <v>0.00681526493281126</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0001401019108016044</v>
+        <v>0.003099430818110704</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0004120779340155423</v>
+        <v>0.006601316854357719</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.0002244530769530684</v>
+        <v>0.005153229925781488</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.0002574184036348015</v>
+        <v>0.01213245652616024</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0005714208818972111</v>
+        <v>0.007739342283457518</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0002568881609477103</v>
+        <v>0.01088940072804689</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0002401087986072525</v>
+        <v>0.006793731357902288</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.0001587971346452832</v>
+        <v>0.005568095482885838</v>
       </c>
       <c r="FW7" t="n">
-        <v>2.507313183741644e-05</v>
+        <v>0.02017772756516933</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0002651479444466531</v>
+        <v>0.001568661187775433</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.0009261271916329861</v>
+        <v>0.003062502481043339</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0002670289250090718</v>
+        <v>0.004765673074871302</v>
       </c>
       <c r="GA7" t="n">
-        <v>8.003777475096285e-05</v>
+        <v>0.007467935793101788</v>
       </c>
       <c r="GB7" t="n">
-        <v>1.028632868838031e-05</v>
+        <v>0.009865880943834782</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0003160198975820094</v>
+        <v>0.006682851351797581</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.0006541779730468988</v>
+        <v>0.01094303466379642</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.001321158255450428</v>
+        <v>0.00472948094829917</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0001385036885039881</v>
+        <v>0.006157262716442347</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0001849523687269539</v>
+        <v>9.758234955370426e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4982,1140 +4982,1140 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.914637337563363e-09</v>
+        <v>2.118339104129063e-08</v>
       </c>
       <c r="B9" t="n">
-        <v>4.789491914181099e-09</v>
+        <v>9.876837481215262e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.425180860108014e-10</v>
+        <v>3.134077886102205e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>9.362485897668194e-09</v>
+        <v>4.408751408391254e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.553423028572865e-10</v>
+        <v>6.923315964968424e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.610389127077894e-10</v>
+        <v>6.945899855281823e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.237477785855702e-10</v>
+        <v>6.588766865434081e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.127293229405637e-10</v>
+        <v>1.01175437805523e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>3.491788802545415e-10</v>
+        <v>9.620566565615718e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>2.77575495921667e-09</v>
+        <v>1.222518974941522e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.458758974199782e-09</v>
+        <v>1.23734253065777e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>1.356834505861215e-10</v>
+        <v>6.024997389886266e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>5.477776898743514e-09</v>
+        <v>9.172805448542931e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.493775769745298e-09</v>
+        <v>1.113771901373184e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>3.515403301790343e-09</v>
+        <v>8.991777633582387e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>1.273493976938767e-09</v>
+        <v>5.247413525921729e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.62120436467228e-09</v>
+        <v>4.300472866702876e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>1.485223888320064e-10</v>
+        <v>3.584865382322278e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.188867476686895e-10</v>
+        <v>6.45901465645693e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>7.429870052533261e-10</v>
+        <v>6.949143482870568e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>6.043276989942115e-10</v>
+        <v>1.313727082674632e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.002960516506619e-10</v>
+        <v>2.038499502532432e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.579257835615522e-09</v>
+        <v>1.449445896639645e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>4.415941501356713e-10</v>
+        <v>1.90384206177896e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.140050663930083e-09</v>
+        <v>2.255436015730083e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.280378052528121e-11</v>
+        <v>1.227404311521241e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.393668069837872e-09</v>
+        <v>6.956826670290184e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.029326623935845e-10</v>
+        <v>6.125342011387147e-09</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.235416656810486e-10</v>
+        <v>2.056701653430082e-08</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.045497353250994e-11</v>
+        <v>1.567001817193159e-08</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.109298541912551e-09</v>
+        <v>3.409317272939916e-08</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.605062860399187e-09</v>
+        <v>8.107677018642789e-08</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.316730946498978e-09</v>
+        <v>5.866768404416689e-08</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.290346187322939e-10</v>
+        <v>9.557902025392195e-09</v>
       </c>
       <c r="AI9" t="n">
-        <v>7.222694664577034e-10</v>
+        <v>7.244990740673529e-08</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.756726708546097e-10</v>
+        <v>1.529367743557941e-10</v>
       </c>
       <c r="AK9" t="n">
-        <v>6.510886274568861e-10</v>
+        <v>4.98177099572672e-09</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.105691507940492e-10</v>
+        <v>2.966462453457552e-08</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.170304934714153e-10</v>
+        <v>2.302846624502308e-08</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.582840968352485e-10</v>
+        <v>1.23661827444721e-08</v>
       </c>
       <c r="AO9" t="n">
-        <v>4.905134076693685e-10</v>
+        <v>1.91263858084767e-08</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.021362132178297e-10</v>
+        <v>3.352975852521922e-08</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.224396917187676e-09</v>
+        <v>1.180096820263543e-08</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.409749870288749e-10</v>
+        <v>1.782947300910109e-08</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.398453599234301e-10</v>
+        <v>3.566140271971108e-09</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.330751620010062e-10</v>
+        <v>1.027675988751753e-08</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.082161637024683e-09</v>
+        <v>1.135839653443327e-07</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.367287517210606e-11</v>
+        <v>3.414783833477486e-08</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.61492991096668e-09</v>
+        <v>2.35962573924553e-08</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.016574824319605e-09</v>
+        <v>9.445707149779992e-08</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.272784377892577e-10</v>
+        <v>7.488139885936107e-08</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.558828397589366e-10</v>
+        <v>5.601510810748778e-09</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.73860745245058e-10</v>
+        <v>1.346019296022405e-09</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.71124248105059e-09</v>
+        <v>3.9641134819135e-09</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.141258421100133e-09</v>
+        <v>2.637863794063833e-08</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.349971245900861e-10</v>
+        <v>3.632631973005118e-09</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.224931929452396e-10</v>
+        <v>2.618785011065938e-08</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.745407814065743e-10</v>
+        <v>3.011202309721739e-08</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.300127006054197e-09</v>
+        <v>3.211777155343043e-08</v>
       </c>
       <c r="BH9" t="n">
-        <v>1.235225116635874e-10</v>
+        <v>1.690826589850758e-09</v>
       </c>
       <c r="BI9" t="n">
-        <v>9.062154360250929e-10</v>
+        <v>8.51621351216636e-09</v>
       </c>
       <c r="BJ9" t="n">
-        <v>3.782220314718643e-09</v>
+        <v>7.449310857055025e-08</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.081682104997483e-10</v>
+        <v>2.805103704872636e-08</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.001740135286866e-09</v>
+        <v>1.658529491521676e-08</v>
       </c>
       <c r="BM9" t="n">
-        <v>4.501850281446451e-10</v>
+        <v>5.588028528791256e-08</v>
       </c>
       <c r="BN9" t="n">
-        <v>7.757632314309149e-10</v>
+        <v>8.538329154816893e-09</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.040523223139189e-09</v>
+        <v>1.625517853653946e-08</v>
       </c>
       <c r="BP9" t="n">
-        <v>2.410426580556901e-10</v>
+        <v>5.659043367245431e-08</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.409315967901506e-10</v>
+        <v>2.057151782253186e-08</v>
       </c>
       <c r="BR9" t="n">
-        <v>4.659986840849228e-10</v>
+        <v>4.050117752285587e-08</v>
       </c>
       <c r="BS9" t="n">
-        <v>3.142061610894586e-10</v>
+        <v>1.602831645186598e-08</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.176734206915114e-11</v>
+        <v>6.190637336089821e-09</v>
       </c>
       <c r="BU9" t="n">
-        <v>8.523445838015675e-12</v>
+        <v>7.268299739848771e-09</v>
       </c>
       <c r="BV9" t="n">
-        <v>1.541623717571383e-09</v>
+        <v>7.216310393687309e-08</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.639168328322228e-10</v>
+        <v>1.080484146598337e-08</v>
       </c>
       <c r="BX9" t="n">
-        <v>1.286554529578154e-09</v>
+        <v>6.175588040946423e-09</v>
       </c>
       <c r="BY9" t="n">
-        <v>5.426546989539816e-10</v>
+        <v>2.093007900327848e-08</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.633573023164587e-12</v>
+        <v>5.780153244927533e-08</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.621385137262621e-09</v>
+        <v>3.213793320355762e-08</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.860451568473479e-10</v>
+        <v>1.251149850389766e-08</v>
       </c>
       <c r="CC9" t="n">
-        <v>1.414967032431491e-09</v>
+        <v>1.928234993897604e-08</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.714029167018907e-10</v>
+        <v>2.09570183429264e-09</v>
       </c>
       <c r="CE9" t="n">
-        <v>8.358412850739683e-10</v>
+        <v>3.557621397476396e-08</v>
       </c>
       <c r="CF9" t="n">
-        <v>9.086387753320935e-10</v>
+        <v>5.748545195416455e-09</v>
       </c>
       <c r="CG9" t="n">
-        <v>7.845394889294255e-10</v>
+        <v>1.253489578800782e-08</v>
       </c>
       <c r="CH9" t="n">
-        <v>7.136881641223169e-10</v>
+        <v>3.335029319373461e-08</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.782697461871763e-10</v>
+        <v>2.748029004351338e-08</v>
       </c>
       <c r="CJ9" t="n">
-        <v>5.613063902565329e-10</v>
+        <v>2.339575200238642e-10</v>
       </c>
       <c r="CK9" t="n">
-        <v>4.07185646311703e-10</v>
+        <v>9.345564322416067e-09</v>
       </c>
       <c r="CL9" t="n">
-        <v>9.458664962380681e-10</v>
+        <v>7.574920690700537e-10</v>
       </c>
       <c r="CM9" t="n">
-        <v>3.603216336411919e-10</v>
+        <v>5.864316676706949e-08</v>
       </c>
       <c r="CN9" t="n">
-        <v>5.747187170612733e-10</v>
+        <v>7.206985230823193e-08</v>
       </c>
       <c r="CO9" t="n">
-        <v>8.137497620186451e-11</v>
+        <v>5.903816102659221e-08</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.784022123947238e-09</v>
+        <v>3.351600952328226e-08</v>
       </c>
       <c r="CQ9" t="n">
-        <v>1.604392951826128e-09</v>
+        <v>1.124086601578256e-08</v>
       </c>
       <c r="CR9" t="n">
-        <v>5.500572775041235e-10</v>
+        <v>5.47112399829075e-08</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.049954456711077e-09</v>
+        <v>4.139411657888559e-08</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.859818826195237e-09</v>
+        <v>8.835673526164101e-09</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.80790410420073e-10</v>
+        <v>2.695655254569829e-09</v>
       </c>
       <c r="CV9" t="n">
-        <v>5.105689759865584e-10</v>
+        <v>2.342221305795533e-09</v>
       </c>
       <c r="CW9" t="n">
-        <v>6.969028132353117e-10</v>
+        <v>2.900476658851403e-08</v>
       </c>
       <c r="CX9" t="n">
-        <v>6.809053321177316e-10</v>
+        <v>2.131687271145211e-09</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.516640146803638e-09</v>
+        <v>2.097293538838585e-08</v>
       </c>
       <c r="CZ9" t="n">
-        <v>8.495687486842485e-10</v>
+        <v>3.765893552554189e-08</v>
       </c>
       <c r="DA9" t="n">
-        <v>3.086884914349497e-10</v>
+        <v>2.480611627220242e-08</v>
       </c>
       <c r="DB9" t="n">
-        <v>5.584346873810375e-10</v>
+        <v>4.991326907344273e-09</v>
       </c>
       <c r="DC9" t="n">
-        <v>4.444226375799332e-10</v>
+        <v>7.569644466798309e-09</v>
       </c>
       <c r="DD9" t="n">
-        <v>7.179050132144482e-10</v>
+        <v>5.76718894862438e-10</v>
       </c>
       <c r="DE9" t="n">
-        <v>5.198075858636741e-10</v>
+        <v>8.800945749953826e-09</v>
       </c>
       <c r="DF9" t="n">
-        <v>8.107576277005535e-10</v>
+        <v>6.603601221399913e-09</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.372109397796862e-09</v>
+        <v>7.077940011868122e-09</v>
       </c>
       <c r="DH9" t="n">
-        <v>7.052936012996724e-09</v>
+        <v>1.63520272877804e-08</v>
       </c>
       <c r="DI9" t="n">
-        <v>2.870380155783891e-09</v>
+        <v>1.434916541143139e-08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.033465618112018e-10</v>
+        <v>2.50001654933385e-08</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.002766869540039e-09</v>
+        <v>1.203150468143122e-09</v>
       </c>
       <c r="DL9" t="n">
-        <v>3.643331636382641e-09</v>
+        <v>6.154884601983213e-08</v>
       </c>
       <c r="DM9" t="n">
-        <v>4.39359548742857e-10</v>
+        <v>1.080216893711849e-08</v>
       </c>
       <c r="DN9" t="n">
-        <v>3.908578738442969e-10</v>
+        <v>2.284617828252067e-08</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.210266774633652e-11</v>
+        <v>2.936522491836513e-08</v>
       </c>
       <c r="DP9" t="n">
-        <v>1.618120082369501e-09</v>
+        <v>1.045246111885945e-08</v>
       </c>
       <c r="DQ9" t="n">
-        <v>2.286221489899987e-10</v>
+        <v>2.095714712879726e-10</v>
       </c>
       <c r="DR9" t="n">
-        <v>1.335352273201806e-09</v>
+        <v>8.397291750839031e-09</v>
       </c>
       <c r="DS9" t="n">
-        <v>1.325873189017557e-09</v>
+        <v>2.551735889255724e-08</v>
       </c>
       <c r="DT9" t="n">
-        <v>4.02407052124687e-10</v>
+        <v>1.98019289854301e-08</v>
       </c>
       <c r="DU9" t="n">
-        <v>5.757589197075141e-11</v>
+        <v>2.481814043164832e-08</v>
       </c>
       <c r="DV9" t="n">
-        <v>1.617619926896907e-09</v>
+        <v>8.794396322286957e-09</v>
       </c>
       <c r="DW9" t="n">
-        <v>9.062252059877096e-10</v>
+        <v>8.900218340102128e-09</v>
       </c>
       <c r="DX9" t="n">
-        <v>5.4882720590399e-10</v>
+        <v>1.84381558909763e-08</v>
       </c>
       <c r="DY9" t="n">
-        <v>1.811743088886431e-09</v>
+        <v>3.052015173921063e-08</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1.131338842053076e-10</v>
+        <v>5.12639619643096e-09</v>
       </c>
       <c r="EA9" t="n">
-        <v>1.562325491200056e-09</v>
+        <v>6.642594740924324e-08</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.699615781447505e-09</v>
+        <v>7.764512588437356e-09</v>
       </c>
       <c r="EC9" t="n">
-        <v>4.630413552586532e-10</v>
+        <v>1.746448496930952e-08</v>
       </c>
       <c r="ED9" t="n">
-        <v>3.656283886765976e-10</v>
+        <v>3.295934902780573e-08</v>
       </c>
       <c r="EE9" t="n">
-        <v>1.507128866151675e-10</v>
+        <v>4.496468974934942e-08</v>
       </c>
       <c r="EF9" t="n">
-        <v>2.897039275140401e-10</v>
+        <v>5.54049073286933e-09</v>
       </c>
       <c r="EG9" t="n">
-        <v>2.595343107092418e-10</v>
+        <v>3.774605517037344e-09</v>
       </c>
       <c r="EH9" t="n">
-        <v>8.300464482413616e-11</v>
+        <v>2.652209829534513e-08</v>
       </c>
       <c r="EI9" t="n">
-        <v>1.081821632276103e-09</v>
+        <v>2.410081911818907e-08</v>
       </c>
       <c r="EJ9" t="n">
-        <v>8.266097251130589e-10</v>
+        <v>2.831583501006207e-08</v>
       </c>
       <c r="EK9" t="n">
-        <v>4.226366756565625e-10</v>
+        <v>2.513036712059602e-08</v>
       </c>
       <c r="EL9" t="n">
-        <v>1.078078515348579e-09</v>
+        <v>9.388045896230324e-10</v>
       </c>
       <c r="EM9" t="n">
-        <v>2.943325028148536e-10</v>
+        <v>9.847603621437884e-09</v>
       </c>
       <c r="EN9" t="n">
-        <v>5.118645507451447e-10</v>
+        <v>2.532635079433021e-08</v>
       </c>
       <c r="EO9" t="n">
-        <v>3.123773462121449e-10</v>
+        <v>6.192311996500166e-09</v>
       </c>
       <c r="EP9" t="n">
-        <v>1.335246635481013e-10</v>
+        <v>2.475365690202125e-08</v>
       </c>
       <c r="EQ9" t="n">
-        <v>5.362368327155309e-10</v>
+        <v>7.097601617545024e-09</v>
       </c>
       <c r="ER9" t="n">
-        <v>2.409476507203578e-10</v>
+        <v>2.048856551084555e-08</v>
       </c>
       <c r="ES9" t="n">
-        <v>2.73963474128891e-09</v>
+        <v>1.450024456062238e-08</v>
       </c>
       <c r="ET9" t="n">
-        <v>6.618504633237876e-10</v>
+        <v>3.106029566879442e-08</v>
       </c>
       <c r="EU9" t="n">
-        <v>2.342991078929657e-10</v>
+        <v>6.074214908835529e-09</v>
       </c>
       <c r="EV9" t="n">
-        <v>1.846650277137485e-09</v>
+        <v>1.075583178078432e-08</v>
       </c>
       <c r="EW9" t="n">
-        <v>2.208522531521595e-10</v>
+        <v>3.18682928934777e-08</v>
       </c>
       <c r="EX9" t="n">
-        <v>3.345091426076863e-10</v>
+        <v>8.37343860915496e-10</v>
       </c>
       <c r="EY9" t="n">
-        <v>7.00086544291878e-10</v>
+        <v>4.080922977323098e-08</v>
       </c>
       <c r="EZ9" t="n">
-        <v>7.129730694721559e-10</v>
+        <v>5.613121967229517e-09</v>
       </c>
       <c r="FA9" t="n">
-        <v>1.227773105405561e-09</v>
+        <v>2.015960376411385e-08</v>
       </c>
       <c r="FB9" t="n">
-        <v>4.763489047654446e-10</v>
+        <v>2.888049266402959e-08</v>
       </c>
       <c r="FC9" t="n">
-        <v>2.8897489956492e-10</v>
+        <v>3.002858761647076e-08</v>
       </c>
       <c r="FD9" t="n">
-        <v>6.138674568667568e-10</v>
+        <v>6.579389921768097e-09</v>
       </c>
       <c r="FE9" t="n">
-        <v>4.107129636388152e-10</v>
+        <v>2.613422367403473e-09</v>
       </c>
       <c r="FF9" t="n">
-        <v>9.555382041170901e-10</v>
+        <v>1.21260921304156e-08</v>
       </c>
       <c r="FG9" t="n">
-        <v>6.117356621260228e-10</v>
+        <v>2.668550536100156e-08</v>
       </c>
       <c r="FH9" t="n">
-        <v>6.344593184159919e-10</v>
+        <v>6.717922218513195e-09</v>
       </c>
       <c r="FI9" t="n">
-        <v>1.8395410750216e-09</v>
+        <v>2.622703654253655e-08</v>
       </c>
       <c r="FJ9" t="n">
-        <v>2.515276653625165e-09</v>
+        <v>4.474035808499366e-09</v>
       </c>
       <c r="FK9" t="n">
-        <v>6.054454715354041e-10</v>
+        <v>3.120542491075184e-09</v>
       </c>
       <c r="FL9" t="n">
-        <v>4.673228470863933e-11</v>
+        <v>4.8428319132654e-09</v>
       </c>
       <c r="FM9" t="n">
-        <v>1.081097544819443e-09</v>
+        <v>4.584948420927049e-09</v>
       </c>
       <c r="FN9" t="n">
-        <v>8.228662196074765e-10</v>
+        <v>3.104827683841904e-08</v>
       </c>
       <c r="FO9" t="n">
-        <v>3.331872278078407e-10</v>
+        <v>5.769194189042537e-08</v>
       </c>
       <c r="FP9" t="n">
-        <v>2.999238357670464e-11</v>
+        <v>3.713904916935462e-08</v>
       </c>
       <c r="FQ9" t="n">
-        <v>1.482408418240766e-09</v>
+        <v>2.434825008279518e-09</v>
       </c>
       <c r="FR9" t="n">
-        <v>1.382382958103889e-10</v>
+        <v>5.468140429343293e-08</v>
       </c>
       <c r="FS9" t="n">
-        <v>1.170009200635036e-09</v>
+        <v>2.962610423651313e-08</v>
       </c>
       <c r="FT9" t="n">
-        <v>2.047089830981008e-09</v>
+        <v>1.271553617954169e-08</v>
       </c>
       <c r="FU9" t="n">
-        <v>1.542479477478764e-10</v>
+        <v>3.640260759496527e-09</v>
       </c>
       <c r="FV9" t="n">
-        <v>1.44692452463957e-10</v>
+        <v>3.772197487705853e-08</v>
       </c>
       <c r="FW9" t="n">
-        <v>1.097341106870431e-09</v>
+        <v>7.395858858672e-08</v>
       </c>
       <c r="FX9" t="n">
-        <v>4.481312543269667e-10</v>
+        <v>8.242456495111128e-09</v>
       </c>
       <c r="FY9" t="n">
-        <v>1.687334494349102e-09</v>
+        <v>1.234808877370597e-08</v>
       </c>
       <c r="FZ9" t="n">
-        <v>4.24712182089948e-10</v>
+        <v>9.119801802626171e-09</v>
       </c>
       <c r="GA9" t="n">
-        <v>2.150797734357113e-10</v>
+        <v>2.269406351729231e-08</v>
       </c>
       <c r="GB9" t="n">
-        <v>7.11551095822216e-11</v>
+        <v>2.164822987538173e-08</v>
       </c>
       <c r="GC9" t="n">
-        <v>2.238664364995202e-09</v>
+        <v>2.174025226509002e-08</v>
       </c>
       <c r="GD9" t="n">
-        <v>5.663408630951494e-10</v>
+        <v>6.933723284419102e-08</v>
       </c>
       <c r="GE9" t="n">
-        <v>3.49088824513899e-09</v>
+        <v>3.64135104291563e-08</v>
       </c>
       <c r="GF9" t="n">
-        <v>3.814503712895601e-10</v>
+        <v>2.676076604757327e-08</v>
       </c>
       <c r="GG9" t="n">
-        <v>1.676660699168053e-09</v>
+        <v>4.282130650068439e-09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0003113914281129837</v>
+        <v>0.0195029079914093</v>
       </c>
       <c r="B10" t="n">
-        <v>0.002704128157347441</v>
+        <v>0.04277702793478966</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001628963073017076</v>
+        <v>0.04972248896956444</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001450830604881048</v>
+        <v>0.01754098944365978</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0001635863591218367</v>
+        <v>0.1050783842802048</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002090363297611475</v>
+        <v>0.06179545074701309</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001673524384386837</v>
+        <v>0.0557512566447258</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0005947574391029775</v>
+        <v>0.06335313618183136</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001105337505578063</v>
+        <v>0.006881454959511757</v>
       </c>
       <c r="J10" t="n">
-        <v>0.000542200286872685</v>
+        <v>0.05889055877923965</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002136528491973877</v>
+        <v>0.1828155368566513</v>
       </c>
       <c r="L10" t="n">
-        <v>4.967648783349432e-05</v>
+        <v>0.04638445377349854</v>
       </c>
       <c r="M10" t="n">
-        <v>0.001384645467624068</v>
+        <v>0.01260687783360481</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0002693996648304164</v>
+        <v>0.1308207660913467</v>
       </c>
       <c r="O10" t="n">
-        <v>0.002098436001688242</v>
+        <v>0.09694482386112213</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0001243162405444309</v>
+        <v>0.1414703130722046</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0002153554814867675</v>
+        <v>0.04198889806866646</v>
       </c>
       <c r="R10" t="n">
-        <v>9.434428648091853e-05</v>
+        <v>0.001839908887632191</v>
       </c>
       <c r="S10" t="n">
-        <v>5.566791514866054e-05</v>
+        <v>0.02652273885905743</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0004074554599355906</v>
+        <v>0.01325393095612526</v>
       </c>
       <c r="U10" t="n">
-        <v>4.742711462313309e-05</v>
+        <v>0.02664258889853954</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0004752794047817588</v>
+        <v>0.05214810743927956</v>
       </c>
       <c r="W10" t="n">
-        <v>9.278808647650294e-06</v>
+        <v>0.06164483353495598</v>
       </c>
       <c r="X10" t="n">
-        <v>3.7736685044365e-05</v>
+        <v>0.01126390881836414</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002411589084658772</v>
+        <v>0.02123306691646576</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.20269454177469e-05</v>
+        <v>0.06791739910840988</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0003497660800348967</v>
+        <v>0.02785821817815304</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.699034853838384e-05</v>
+        <v>0.0838390439748764</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0003024444449692965</v>
+        <v>0.01001411303877831</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.75834281637799e-05</v>
+        <v>0.01987388916313648</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0001163034030469134</v>
+        <v>0.01629388332366943</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0001207335299113765</v>
+        <v>0.08468916267156601</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.217988705728203e-05</v>
+        <v>0.04233430698513985</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.00038188073085621</v>
+        <v>0.06416744738817215</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.43999386637006e-05</v>
+        <v>0.08321948349475861</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.528450229670852e-05</v>
+        <v>0.008685632608830929</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0002986787003464997</v>
+        <v>0.01564636081457138</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0003175303572788835</v>
+        <v>0.006788562051951885</v>
       </c>
       <c r="AM10" t="n">
-        <v>5.584710743278265e-05</v>
+        <v>0.01734481751918793</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0002739459159784019</v>
+        <v>0.04003921896219254</v>
       </c>
       <c r="AO10" t="n">
-        <v>9.795801452128217e-05</v>
+        <v>0.0597706101834774</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0004263326991349459</v>
+        <v>0.003264293540269136</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.512965723639354e-05</v>
+        <v>0.004886615090072155</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0001123749607359059</v>
+        <v>0.06027405336499214</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0002028846793109551</v>
+        <v>0.002870944095775485</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0001902354415506124</v>
+        <v>0.0285504087805748</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.001903840922750533</v>
+        <v>0.2178781479597092</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0001615291548660025</v>
+        <v>0.08147445321083069</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.104717274662107e-06</v>
+        <v>0.008729016408324242</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.000210415106266737</v>
+        <v>0.02551137842237949</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.001155389589257538</v>
+        <v>0.09153967350721359</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0001114020051318221</v>
+        <v>0.008543781004846096</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0003817038086708635</v>
+        <v>0.04561785981059074</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0003705584385897964</v>
+        <v>0.01550437323749065</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0001118194195441902</v>
+        <v>0.002590201795101166</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0005754187586717308</v>
+        <v>0.06723541766405106</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0006310290191322565</v>
+        <v>0.002787285950034857</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0007663901196792722</v>
+        <v>0.09334571659564972</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.000635060016065836</v>
+        <v>0.09807377308607101</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0007030048873275518</v>
+        <v>0.03886142000555992</v>
       </c>
       <c r="BI10" t="n">
-        <v>7.816003926564008e-05</v>
+        <v>0.04717054963111877</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0004885274101980031</v>
+        <v>0.1030511409044266</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.699398363707587e-05</v>
+        <v>0.02793856337666512</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0002911703195422888</v>
+        <v>0.02208110690116882</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0007844326901249588</v>
+        <v>0.08754147589206696</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.000198194247786887</v>
+        <v>0.02561201155185699</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0003705246781464666</v>
+        <v>0.09208995848894119</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0004361897008493543</v>
+        <v>0.07215937972068787</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.456103655073093e-05</v>
+        <v>0.0009740926907397807</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0002602189488243312</v>
+        <v>0.02849945425987244</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0001875944726634771</v>
+        <v>0.07255877554416656</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.999118729960173e-05</v>
+        <v>0.002152744214981794</v>
       </c>
       <c r="BU10" t="n">
-        <v>7.829074456822127e-05</v>
+        <v>0.04794088006019592</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.0009745642892085016</v>
+        <v>0.1083627641201019</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.0001449447881896049</v>
+        <v>0.04881690442562103</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0001130215387092903</v>
+        <v>0.04980958625674248</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.8169050286524e-05</v>
+        <v>0.04772917926311493</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0002442765398882329</v>
+        <v>0.01371481642127037</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0003799374389927834</v>
+        <v>0.009158270433545113</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.000152244494529441</v>
+        <v>0.04008704051375389</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0002039413520833477</v>
+        <v>0.006641020998358727</v>
       </c>
       <c r="CD10" t="n">
-        <v>9.305395360570401e-05</v>
+        <v>0.01990577206015587</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0004837554006371647</v>
+        <v>0.01599243097007275</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0001906240941025317</v>
+        <v>0.005334184039384127</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0001552814646856859</v>
+        <v>0.005827018525451422</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0001566803985042498</v>
+        <v>0.04130930826067924</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0003661876835394651</v>
+        <v>0.02546443976461887</v>
       </c>
       <c r="CJ10" t="n">
-        <v>5.729057374992408e-05</v>
+        <v>0.001756053999997675</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0001406555238645524</v>
+        <v>0.004691177979111671</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0001372546685161069</v>
+        <v>0.0107552157714963</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0003318477829452604</v>
+        <v>0.02091576531529427</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0003497582802083343</v>
+        <v>0.1254801899194717</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.418136525899172e-05</v>
+        <v>0.04452516138553619</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0003929862286895514</v>
+        <v>0.08040435612201691</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0001166924048447981</v>
+        <v>0.08116994798183441</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0001466305984649807</v>
+        <v>0.02204326167702675</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.00011695601278916</v>
+        <v>0.05908584222197533</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0003763660206459463</v>
+        <v>0.03347131609916687</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0001464472006773576</v>
+        <v>0.01642557419836521</v>
       </c>
       <c r="CV10" t="n">
-        <v>7.471870048902929e-05</v>
+        <v>0.01270801015198231</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0003726680297404528</v>
+        <v>0.01669280044734478</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0001835230941651389</v>
+        <v>0.005431014113128185</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.000301972555462271</v>
+        <v>0.02118885517120361</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0001375992869725451</v>
+        <v>0.0249625351279974</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0003507680376060307</v>
+        <v>0.02641670219600201</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0001146640788647346</v>
+        <v>0.01062583085149527</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0002849600277841091</v>
+        <v>0.009823705069720745</v>
       </c>
       <c r="DD10" t="n">
-        <v>6.580348417628556e-05</v>
+        <v>0.01544757559895515</v>
       </c>
       <c r="DE10" t="n">
-        <v>7.210300827864558e-05</v>
+        <v>0.03765193372964859</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0007621578988619149</v>
+        <v>0.03676611185073853</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0001962139940587804</v>
+        <v>0.08152274042367935</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0007381842588074505</v>
+        <v>0.08031174540519714</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0001820502220652997</v>
+        <v>0.04126860201358795</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0002963506558444351</v>
+        <v>0.03376617655158043</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0002628829970490187</v>
+        <v>0.02217242494225502</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.000536530336830765</v>
+        <v>0.001029854407534003</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0003503380867186934</v>
+        <v>0.006380927283316851</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0001630032638786361</v>
+        <v>0.0364590510725975</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0003031404048670083</v>
+        <v>0.04765776917338371</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0002652723924256861</v>
+        <v>0.005207997746765614</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0002679431345313787</v>
+        <v>0.02717209048569202</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.000160620576934889</v>
+        <v>0.05726629495620728</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0001795736025087535</v>
+        <v>0.02726660668849945</v>
       </c>
       <c r="DT10" t="n">
-        <v>1.627077290322632e-05</v>
+        <v>0.01595025509595871</v>
       </c>
       <c r="DU10" t="n">
-        <v>4.383948544273153e-05</v>
+        <v>0.1079548522830009</v>
       </c>
       <c r="DV10" t="n">
-        <v>7.745912444079295e-05</v>
+        <v>0.01125647779554129</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0001394632417941466</v>
+        <v>0.05612233281135559</v>
       </c>
       <c r="DX10" t="n">
-        <v>1.668483491812367e-05</v>
+        <v>0.02988271415233612</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0002676567528396845</v>
+        <v>0.05485811829566956</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.255152842029929e-05</v>
+        <v>0.03571757674217224</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0001706782495602965</v>
+        <v>0.004752709530293941</v>
       </c>
       <c r="EB10" t="n">
-        <v>8.519100811099634e-05</v>
+        <v>0.00227699032984674</v>
       </c>
       <c r="EC10" t="n">
-        <v>6.822826253483072e-05</v>
+        <v>0.05178960785269737</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0001749141374602914</v>
+        <v>0.03613785654306412</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0002644262567628175</v>
+        <v>0.0004405495710670948</v>
       </c>
       <c r="EF10" t="n">
-        <v>1.829158281907439e-05</v>
+        <v>0.02349799498915672</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0002137351257260889</v>
+        <v>0.009570310823619366</v>
       </c>
       <c r="EH10" t="n">
-        <v>4.249854100635275e-05</v>
+        <v>0.01621406711637974</v>
       </c>
       <c r="EI10" t="n">
-        <v>1.132962643168867e-05</v>
+        <v>0.03057849407196045</v>
       </c>
       <c r="EJ10" t="n">
-        <v>2.017917722696438e-05</v>
+        <v>0.02101578749716282</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.000199892747332342</v>
+        <v>0.02774418704211712</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0001331709063379094</v>
+        <v>0.002661272417753935</v>
       </c>
       <c r="EM10" t="n">
-        <v>8.765023085288703e-05</v>
+        <v>0.02508244849741459</v>
       </c>
       <c r="EN10" t="n">
-        <v>9.841164865065366e-05</v>
+        <v>0.01487924996763468</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0001300000876653939</v>
+        <v>0.0206018965691328</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0002217414294136688</v>
+        <v>0.04108772054314613</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0001346084027318284</v>
+        <v>0.002207192592322826</v>
       </c>
       <c r="ER10" t="n">
-        <v>9.780909022083506e-05</v>
+        <v>0.02345544099807739</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.000129444117192179</v>
+        <v>0.03332315757870674</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0002414514019619673</v>
+        <v>0.001603227574378252</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0001782891049515456</v>
+        <v>0.03215916082262993</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0004282624868210405</v>
+        <v>0.04078606516122818</v>
       </c>
       <c r="EW10" t="n">
-        <v>1.255803090316476e-05</v>
+        <v>0.0018987194634974</v>
       </c>
       <c r="EX10" t="n">
-        <v>7.424653449561447e-05</v>
+        <v>0.01877472922205925</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0003580648335628211</v>
+        <v>0.01852643303573132</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0001017448739730753</v>
+        <v>0.009453384205698967</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0001594276691321284</v>
+        <v>0.007784449961036444</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0001273657398996875</v>
+        <v>0.02506075985729694</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0003380518173798919</v>
+        <v>0.03605559095740318</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0001454223820473999</v>
+        <v>0.007874814793467522</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0001377309672534466</v>
+        <v>0.008266044780611992</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0001719552965369076</v>
+        <v>0.01129923481494188</v>
       </c>
       <c r="FG10" t="n">
-        <v>6.743730773450807e-05</v>
+        <v>0.04282701015472412</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0001094989493140019</v>
+        <v>0.01949535310268402</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0001636340166442096</v>
+        <v>0.02554246969521046</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.00012149410758866</v>
+        <v>0.07446499913930893</v>
       </c>
       <c r="FK10" t="n">
-        <v>4.583477493724786e-05</v>
+        <v>0.05587316676974297</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0002369697467656806</v>
+        <v>0.01950264163315296</v>
       </c>
       <c r="FM10" t="n">
-        <v>2.60426095337607e-05</v>
+        <v>0.04488152265548706</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0001733308163238689</v>
+        <v>0.02935382723808289</v>
       </c>
       <c r="FO10" t="n">
-        <v>1.757326390361413e-05</v>
+        <v>0.02683451026678085</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.000153167697135359</v>
+        <v>0.01577939093112946</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0002180525480071083</v>
+        <v>0.09467051923274994</v>
       </c>
       <c r="FR10" t="n">
-        <v>5.626838174066506e-06</v>
+        <v>0.01930234581232071</v>
       </c>
       <c r="FS10" t="n">
-        <v>8.389125287067145e-05</v>
+        <v>0.007424525450915098</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0008119302219711244</v>
+        <v>0.1786657422780991</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0002007440489251167</v>
+        <v>0.05191672965884209</v>
       </c>
       <c r="FV10" t="n">
-        <v>5.215204873820767e-05</v>
+        <v>0.0613863505423069</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0003548377135302871</v>
+        <v>0.02167942933738232</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.000168024969752878</v>
+        <v>0.008896004408597946</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0004246051539666951</v>
+        <v>0.01151431165635586</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0001256885443581268</v>
+        <v>0.008659573271870613</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.000146533886436373</v>
+        <v>0.0160707738250494</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0002468583988957107</v>
+        <v>0.06220356002449989</v>
       </c>
       <c r="GC10" t="n">
-        <v>6.90321103320457e-05</v>
+        <v>0.03635365515947342</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0001773940748535097</v>
+        <v>0.02270801924169064</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0007573181064799428</v>
+        <v>0.01220299862325191</v>
       </c>
       <c r="GF10" t="n">
-        <v>6.033353565726429e-05</v>
+        <v>0.03431780263781548</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0002289350522914901</v>
+        <v>0.02588765509426594</v>
       </c>
     </row>
   </sheetData>
